--- a/horarios.xlsx
+++ b/horarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dreame\Desktop\Claude\Dreame\Turnos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3162802A-DA98-4C0B-847F-9337D859093A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73193F81-0317-4C83-B386-A988D5714BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -65,9 +65,6 @@
     <t>KARIN ANDREA NAVIA LILLO</t>
   </si>
   <si>
-    <t>JAVIER ANTONIA VERDUGO JARA</t>
-  </si>
-  <si>
     <t>ROMINA MANSILLA</t>
   </si>
   <si>
@@ -96,6 +93,9 @@
   </si>
   <si>
     <t>Libre</t>
+  </si>
+  <si>
+    <t>LESLIE SCHAAD</t>
   </si>
 </sst>
 </file>
@@ -609,7 +609,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C1" s="15"/>
       <c r="D1" s="15"/>
@@ -708,16 +708,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F4" s="12">
         <v>0.4375</v>
@@ -757,16 +757,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F5" s="12">
         <v>0.4375</v>
@@ -806,16 +806,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F6" s="12">
         <v>0.4375</v>
@@ -861,16 +861,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H7" s="12">
         <v>0.41666666666666669</v>
@@ -904,16 +904,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F8" s="12">
         <v>0.4375</v>
@@ -953,16 +953,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F9" s="12">
         <v>0.4375</v>
@@ -999,19 +999,19 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" s="12">
         <v>0.4375</v>
@@ -1048,19 +1048,19 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F11" s="12">
         <v>0.4375</v>
@@ -1097,7 +1097,7 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="12">
         <v>0.4375</v>
@@ -1112,16 +1112,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H12" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J12" s="12">
         <v>0.41666666666666669</v>
@@ -1146,19 +1146,19 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F13" s="12">
         <v>0.4375</v>
@@ -1193,7 +1193,7 @@
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="12">
         <v>0.4375</v>
@@ -1202,16 +1202,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H14" s="12">
         <v>0.4375</v>
@@ -1240,19 +1240,19 @@
     </row>
     <row r="15" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F15" s="12">
         <v>0.4375</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="18" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
@@ -1386,10 +1386,10 @@
         <v>3</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D21" s="12">
         <v>0.4375</v>
@@ -1422,10 +1422,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N21" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
@@ -1433,10 +1433,10 @@
         <v>4</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D22" s="12">
         <v>0.4375</v>
@@ -1469,10 +1469,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
@@ -1480,10 +1480,10 @@
         <v>5</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D23" s="12">
         <v>0.4375</v>
@@ -1516,10 +1516,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N23" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O23" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
@@ -1527,10 +1527,10 @@
         <v>6</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D24" s="12">
         <v>0.4375</v>
@@ -1563,10 +1563,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O24" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
@@ -1574,10 +1574,10 @@
         <v>7</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D25" s="12">
         <v>0.4375</v>
@@ -1610,10 +1610,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N25" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O25" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
@@ -1621,10 +1621,10 @@
         <v>8</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D26" s="12">
         <v>0.4375</v>
@@ -1657,21 +1657,21 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N26" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O26" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D27" s="12">
         <v>0.4375</v>
@@ -1704,21 +1704,21 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N27" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O27" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D28" s="12">
         <v>0.4375</v>
@@ -1751,21 +1751,21 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N28" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O28" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D29" s="12">
         <v>0.4375</v>
@@ -1798,21 +1798,21 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N29" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O29" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D30" s="12">
         <v>0.4375</v>
@@ -1845,21 +1845,21 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N30" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O30" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D31" s="12">
         <v>0.4375</v>
@@ -1892,21 +1892,21 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N31" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O31" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D32" s="12">
         <v>0.4375</v>
@@ -1939,15 +1939,15 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N32" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O32" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C35" s="15"/>
       <c r="D35" s="15"/>
@@ -2052,10 +2052,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F38" s="12">
         <v>0.4375</v>
@@ -2082,10 +2082,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N38" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O38" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
@@ -2099,10 +2099,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F39" s="12">
         <v>0.4375</v>
@@ -2129,10 +2129,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N39" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O39" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
@@ -2146,10 +2146,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F40" s="12">
         <v>0.4375</v>
@@ -2176,10 +2176,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N40" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O40" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
@@ -2193,10 +2193,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F41" s="12">
         <v>0.4375</v>
@@ -2223,10 +2223,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N41" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O41" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
@@ -2240,10 +2240,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F42" s="12">
         <v>0.4375</v>
@@ -2270,10 +2270,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N42" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O42" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
@@ -2287,10 +2287,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F43" s="12">
         <v>0.4375</v>
@@ -2317,15 +2317,15 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N43" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O43" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B44" s="12">
         <v>0.4375</v>
@@ -2334,10 +2334,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F44" s="12">
         <v>0.4375</v>
@@ -2364,15 +2364,15 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N44" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O44" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B45" s="12">
         <v>0.4375</v>
@@ -2381,10 +2381,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F45" s="12">
         <v>0.4375</v>
@@ -2411,15 +2411,15 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N45" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O45" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B46" s="12">
         <v>0.4375</v>
@@ -2428,10 +2428,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F46" s="12">
         <v>0.4375</v>
@@ -2458,15 +2458,15 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O46" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B47" s="12">
         <v>0.4375</v>
@@ -2475,10 +2475,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F47" s="12">
         <v>0.4375</v>
@@ -2505,15 +2505,15 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N47" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O47" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B48" s="12">
         <v>0.4375</v>
@@ -2522,10 +2522,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F48" s="12">
         <v>0.4375</v>
@@ -2552,15 +2552,15 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N48" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O48" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B49" s="12">
         <v>0.4375</v>
@@ -2569,10 +2569,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F49" s="12">
         <v>0.4375</v>
@@ -2599,15 +2599,15 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N49" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="O49" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B52" s="15" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C52" s="15"/>
       <c r="D52" s="15"/>
@@ -2718,16 +2718,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J55" s="12">
         <v>0.41666666666666669</v>
@@ -2765,16 +2765,16 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J56" s="12">
         <v>0.41666666666666669</v>
@@ -2812,16 +2812,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J57" s="12">
         <v>0.41666666666666669</v>
@@ -2859,16 +2859,16 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J58" s="12">
         <v>0.41666666666666669</v>
@@ -2906,16 +2906,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J59" s="12">
         <v>0.41666666666666669</v>
@@ -2953,16 +2953,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J60" s="12">
         <v>0.41666666666666669</v>
@@ -2985,7 +2985,7 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="B61" s="12">
         <v>0.4375</v>
@@ -3000,16 +3000,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J61" s="12">
         <v>0.41666666666666669</v>
@@ -3032,7 +3032,7 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B62" s="12">
         <v>0.4375</v>
@@ -3047,16 +3047,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J62" s="12">
         <v>0.41666666666666669</v>
@@ -3079,7 +3079,7 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B63" s="12">
         <v>0.4375</v>
@@ -3094,16 +3094,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J63" s="12">
         <v>0.41666666666666669</v>
@@ -3126,7 +3126,7 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B64" s="12">
         <v>0.4375</v>
@@ -3141,16 +3141,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J64" s="12">
         <v>0.41666666666666669</v>
@@ -3173,7 +3173,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B65" s="12">
         <v>0.4375</v>
@@ -3188,16 +3188,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J65" s="12">
         <v>0.41666666666666669</v>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="66" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="14" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B66" s="12">
         <v>0.4375</v>
@@ -3235,16 +3235,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G66" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J66" s="12">
         <v>0.41666666666666669</v>

--- a/horarios.xlsx
+++ b/horarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dreame\Desktop\Claude\Dreame\Turnos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73193F81-0317-4C83-B386-A988D5714BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35CA2F9D-FC15-42D6-B592-212CD1DC6E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,9 +77,6 @@
     <t>SERGIO GALLEGOS</t>
   </si>
   <si>
-    <t>MATIAS PEREZ</t>
-  </si>
-  <si>
     <t>Semana 32</t>
   </si>
   <si>
@@ -95,7 +92,10 @@
     <t>Libre</t>
   </si>
   <si>
-    <t>LESLIE SCHAAD</t>
+    <t>MELISSA MOLINA</t>
+  </si>
+  <si>
+    <t>SAMIRA ALVAREZ</t>
   </si>
 </sst>
 </file>
@@ -609,7 +609,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="15" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1" s="15"/>
       <c r="D1" s="15"/>
@@ -708,16 +708,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F4" s="12">
         <v>0.4375</v>
@@ -757,16 +757,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F5" s="12">
         <v>0.4375</v>
@@ -806,16 +806,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F6" s="12">
         <v>0.4375</v>
@@ -861,16 +861,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H7" s="12">
         <v>0.41666666666666669</v>
@@ -904,16 +904,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F8" s="12">
         <v>0.4375</v>
@@ -953,16 +953,16 @@
         <v>8</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9" s="12">
         <v>0.4375</v>
@@ -1002,16 +1002,16 @@
         <v>19</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F10" s="12">
         <v>0.4375</v>
@@ -1051,16 +1051,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F11" s="12">
         <v>0.4375</v>
@@ -1111,29 +1111,29 @@
       <c r="E12" s="12">
         <v>0.79166666666666663</v>
       </c>
-      <c r="F12" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="J12" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K12" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L12" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M12" s="12">
-        <v>0.83333333333333337</v>
+      <c r="F12" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="G12" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="H12" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I12" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J12" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="L12" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="M12" s="11" t="s">
+        <v>17</v>
       </c>
       <c r="N12" s="12">
         <v>0.41666666666666669</v>
@@ -1149,16 +1149,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F13" s="12">
         <v>0.4375</v>
@@ -1202,16 +1202,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H14" s="12">
         <v>0.4375</v>
@@ -1240,19 +1240,19 @@
     </row>
     <row r="15" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A15" s="14" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F15" s="12">
         <v>0.4375</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="18" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
@@ -1386,10 +1386,10 @@
         <v>3</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D21" s="12">
         <v>0.4375</v>
@@ -1422,10 +1422,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N21" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
@@ -1433,10 +1433,10 @@
         <v>4</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D22" s="12">
         <v>0.4375</v>
@@ -1469,10 +1469,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
@@ -1480,10 +1480,10 @@
         <v>5</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D23" s="12">
         <v>0.4375</v>
@@ -1516,10 +1516,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N23" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O23" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
@@ -1527,10 +1527,10 @@
         <v>6</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D24" s="12">
         <v>0.4375</v>
@@ -1563,10 +1563,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O24" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
@@ -1574,10 +1574,10 @@
         <v>7</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D25" s="12">
         <v>0.4375</v>
@@ -1610,10 +1610,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N25" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O25" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
@@ -1621,10 +1621,10 @@
         <v>8</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D26" s="12">
         <v>0.4375</v>
@@ -1657,10 +1657,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N26" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O26" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
@@ -1668,10 +1668,10 @@
         <v>19</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D27" s="12">
         <v>0.4375</v>
@@ -1704,10 +1704,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N27" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O27" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
@@ -1715,10 +1715,10 @@
         <v>9</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D28" s="12">
         <v>0.4375</v>
@@ -1751,10 +1751,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N28" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O28" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
@@ -1762,10 +1762,10 @@
         <v>10</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D29" s="12">
         <v>0.4375</v>
@@ -1798,10 +1798,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N29" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O29" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
@@ -1809,10 +1809,10 @@
         <v>11</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D30" s="12">
         <v>0.4375</v>
@@ -1845,10 +1845,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N30" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O30" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
@@ -1856,10 +1856,10 @@
         <v>12</v>
       </c>
       <c r="B31" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D31" s="12">
         <v>0.4375</v>
@@ -1892,21 +1892,21 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N31" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O31" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="14" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D32" s="12">
         <v>0.4375</v>
@@ -1939,15 +1939,15 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N32" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O32" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="15" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C35" s="15"/>
       <c r="D35" s="15"/>
@@ -2052,10 +2052,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F38" s="12">
         <v>0.4375</v>
@@ -2082,10 +2082,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N38" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O38" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
@@ -2099,10 +2099,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F39" s="12">
         <v>0.4375</v>
@@ -2129,10 +2129,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N39" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O39" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
@@ -2146,10 +2146,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F40" s="12">
         <v>0.4375</v>
@@ -2176,10 +2176,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N40" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O40" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
@@ -2193,10 +2193,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F41" s="12">
         <v>0.4375</v>
@@ -2223,10 +2223,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N41" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O41" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
@@ -2240,10 +2240,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F42" s="12">
         <v>0.4375</v>
@@ -2270,10 +2270,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N42" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O42" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
@@ -2287,10 +2287,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F43" s="12">
         <v>0.4375</v>
@@ -2317,10 +2317,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N43" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O43" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
@@ -2334,10 +2334,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F44" s="12">
         <v>0.4375</v>
@@ -2364,10 +2364,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N44" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O44" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
@@ -2381,10 +2381,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F45" s="12">
         <v>0.4375</v>
@@ -2411,10 +2411,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N45" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O45" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
@@ -2428,10 +2428,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F46" s="12">
         <v>0.4375</v>
@@ -2458,10 +2458,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O46" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
@@ -2475,10 +2475,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F47" s="12">
         <v>0.4375</v>
@@ -2505,10 +2505,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N47" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O47" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
@@ -2522,10 +2522,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F48" s="12">
         <v>0.4375</v>
@@ -2552,15 +2552,15 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N48" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O48" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="49" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A49" s="14" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B49" s="12">
         <v>0.4375</v>
@@ -2569,10 +2569,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F49" s="12">
         <v>0.4375</v>
@@ -2599,15 +2599,15 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N49" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O49" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="52" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B52" s="15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C52" s="15"/>
       <c r="D52" s="15"/>
@@ -2718,16 +2718,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F55" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J55" s="12">
         <v>0.41666666666666669</v>
@@ -2765,16 +2765,16 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J56" s="12">
         <v>0.41666666666666669</v>
@@ -2812,16 +2812,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F57" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J57" s="12">
         <v>0.41666666666666669</v>
@@ -2859,16 +2859,16 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J58" s="12">
         <v>0.41666666666666669</v>
@@ -2906,16 +2906,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F59" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J59" s="12">
         <v>0.41666666666666669</v>
@@ -2953,16 +2953,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J60" s="12">
         <v>0.41666666666666669</v>
@@ -3000,16 +3000,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J61" s="12">
         <v>0.41666666666666669</v>
@@ -3047,16 +3047,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J62" s="12">
         <v>0.41666666666666669</v>
@@ -3094,16 +3094,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J63" s="12">
         <v>0.41666666666666669</v>
@@ -3141,16 +3141,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J64" s="12">
         <v>0.41666666666666669</v>
@@ -3188,16 +3188,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J65" s="12">
         <v>0.41666666666666669</v>
@@ -3220,7 +3220,7 @@
     </row>
     <row r="66" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A66" s="14" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B66" s="12">
         <v>0.4375</v>
@@ -3235,16 +3235,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G66" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J66" s="12">
         <v>0.41666666666666669</v>

--- a/horarios.xlsx
+++ b/horarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dreame\Desktop\Claude\Dreame\Turnos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35CA2F9D-FC15-42D6-B592-212CD1DC6E3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71C0268-9425-466C-A616-8870E8896F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="21">
   <si>
     <t>Promotor</t>
   </si>
@@ -47,28 +47,7 @@
     <t>Salida</t>
   </si>
   <si>
-    <t>RAFAEL HERNAN BUSTOS MONTALDI</t>
-  </si>
-  <si>
-    <t>GEISSLEN ALYNE ERICES BUSTAMANTE</t>
-  </si>
-  <si>
-    <t>NATALIA PASCALE MARTINEZ MORAGA</t>
-  </si>
-  <si>
-    <t>LISSETTE ALEJANDRA MORALES RIVERA</t>
-  </si>
-  <si>
-    <t>CRISTIAN DANIEL MORALES ARAYA</t>
-  </si>
-  <si>
-    <t>KARIN ANDREA NAVIA LILLO</t>
-  </si>
-  <si>
     <t>ROMINA MANSILLA</t>
-  </si>
-  <si>
-    <t>JORDAN JAVIER RIMMELIN JARA</t>
   </si>
   <si>
     <t>CESAR CASTILLO</t>
@@ -96,6 +75,30 @@
   </si>
   <si>
     <t>SAMIRA ALVAREZ</t>
+  </si>
+  <si>
+    <t>RAFAEL BUSTOS</t>
+  </si>
+  <si>
+    <t>MAXIMILIANO MEDINA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GEISSLEN ERICES </t>
+  </si>
+  <si>
+    <t>LISSETTE MORALES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CRISTIAN MORALES </t>
+  </si>
+  <si>
+    <t>KARIN NAVIA</t>
+  </si>
+  <si>
+    <t>JORDAN RIMMELIN</t>
+  </si>
+  <si>
+    <t>MATIAS BERENGUELA</t>
   </si>
 </sst>
 </file>
@@ -601,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DB7FB46-34C8-4ECD-A089-0D01F6EF7C8B}">
-  <dimension ref="A1:R66"/>
+  <dimension ref="A1:R68"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.33203125" bestFit="1" customWidth="1"/>
@@ -609,7 +612,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="15" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C1" s="15"/>
       <c r="D1" s="15"/>
@@ -705,19 +708,19 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="13" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F4" s="12">
         <v>0.4375</v>
@@ -754,19 +757,19 @@
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F5" s="12">
         <v>0.4375</v>
@@ -803,31 +806,31 @@
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="11" t="s">
-        <v>17</v>
+        <v>16</v>
+      </c>
+      <c r="B6" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C6" s="12">
+        <v>0.79166666666666663</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="G6" s="12">
-        <v>0.79166666666666663</v>
+        <v>10</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>10</v>
       </c>
       <c r="H6" s="12">
-        <v>0.4375</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I6" s="12">
-        <v>0.79166666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="J6" s="12">
         <v>0.41666666666666669</v>
@@ -845,38 +848,38 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="O6" s="12">
-        <v>0.83333333333333337</v>
+        <v>0.77083333333333337</v>
       </c>
       <c r="Q6" s="5"/>
       <c r="R6" s="5"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C7" s="12">
-        <v>0.79166666666666663</v>
+        <v>17</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>10</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="F7" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="G7" s="12">
+        <v>0.79166666666666663</v>
       </c>
       <c r="H7" s="12">
-        <v>0.41666666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="I7" s="12">
-        <v>0.83333333333333337</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="J7" s="12">
         <v>0.41666666666666669</v>
@@ -894,26 +897,26 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="O7" s="12">
-        <v>0.77083333333333337</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="Q7" s="5"/>
       <c r="R7" s="5"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F8" s="12">
         <v>0.4375</v>
@@ -950,19 +953,19 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F9" s="12">
         <v>0.4375</v>
@@ -999,19 +1002,19 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F10" s="12">
         <v>0.4375</v>
@@ -1048,43 +1051,43 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C11" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>17</v>
+        <v>19</v>
+      </c>
+      <c r="B11" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C11" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D11" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="E11" s="12">
+        <v>0.79166666666666663</v>
       </c>
       <c r="F11" s="12">
-        <v>0.4375</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="G11" s="12">
-        <v>0.79166666666666663</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="H11" s="12">
-        <v>0.4375</v>
+        <v>0.41666666666666669</v>
       </c>
       <c r="I11" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="J11" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K11" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L11" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M11" s="12">
-        <v>0.83333333333333337</v>
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J11" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="K11" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="L11" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="M11" s="11" t="s">
+        <v>10</v>
       </c>
       <c r="N11" s="12">
         <v>0.41666666666666669</v>
@@ -1097,43 +1100,43 @@
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="B12" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C12" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D12" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="E12" s="12">
-        <v>0.79166666666666663</v>
+        <v>4</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>10</v>
       </c>
       <c r="F12" s="12">
-        <v>0.41666666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="G12" s="12">
-        <v>0.83333333333333337</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="H12" s="12">
-        <v>0.41666666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="I12" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J12" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="K12" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="L12" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="M12" s="11" t="s">
-        <v>17</v>
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="J12" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K12" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L12" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M12" s="12">
+        <v>0.83333333333333337</v>
       </c>
       <c r="N12" s="12">
         <v>0.41666666666666669</v>
@@ -1141,77 +1144,75 @@
       <c r="O12" s="12">
         <v>0.83333333333333337</v>
       </c>
-      <c r="Q12" s="5"/>
-      <c r="R12" s="5"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C13" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D13" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G13" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H13" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="I13" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="J13" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K13" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L13" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M13" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N13" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="O13" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F13" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="G13" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H13" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="I13" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="J13" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K13" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L13" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M13" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N13" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="O13" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C14" s="12">
-        <v>0.79166666666666663</v>
+      <c r="B14" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C14" s="11" t="s">
+        <v>10</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="F14" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="G14" s="12">
+        <v>0.79166666666666663</v>
       </c>
       <c r="H14" s="12">
         <v>0.4375</v>
@@ -1238,158 +1239,160 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="B15" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C15" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="F15" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="G15" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H15" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="I15" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="J15" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K15" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L15" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M15" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N15" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="O15" s="12">
-        <v>0.83333333333333337</v>
-      </c>
+    <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B17" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
     </row>
     <row r="18" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
-      <c r="L18" s="15"/>
-      <c r="M18" s="15"/>
-      <c r="N18" s="15"/>
-      <c r="O18" s="15"/>
+      <c r="A18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="16">
+        <v>46244</v>
+      </c>
+      <c r="C18" s="17"/>
+      <c r="D18" s="16">
+        <v>46245</v>
+      </c>
+      <c r="E18" s="17"/>
+      <c r="F18" s="16">
+        <v>46246</v>
+      </c>
+      <c r="G18" s="17"/>
+      <c r="H18" s="16">
+        <v>46247</v>
+      </c>
+      <c r="I18" s="17"/>
+      <c r="J18" s="16">
+        <v>46248</v>
+      </c>
+      <c r="K18" s="17"/>
+      <c r="L18" s="16">
+        <v>46249</v>
+      </c>
+      <c r="M18" s="17"/>
+      <c r="N18" s="16">
+        <v>46250</v>
+      </c>
+      <c r="O18" s="17"/>
     </row>
     <row r="19" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B19" s="16">
-        <v>46244</v>
-      </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="16">
-        <v>46245</v>
-      </c>
-      <c r="E19" s="17"/>
-      <c r="F19" s="16">
-        <v>46246</v>
-      </c>
-      <c r="G19" s="17"/>
-      <c r="H19" s="16">
-        <v>46247</v>
-      </c>
-      <c r="I19" s="17"/>
-      <c r="J19" s="16">
-        <v>46248</v>
-      </c>
-      <c r="K19" s="17"/>
-      <c r="L19" s="16">
-        <v>46249</v>
-      </c>
-      <c r="M19" s="17"/>
-      <c r="N19" s="16">
-        <v>46250</v>
-      </c>
-      <c r="O19" s="17"/>
-    </row>
-    <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="2"/>
-      <c r="B20" s="4" t="s">
+      <c r="A19" s="2"/>
+      <c r="B19" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C19" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D19" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E19" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F19" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G20" s="4" t="s">
+      <c r="G19" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H20" s="4" t="s">
+      <c r="H19" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="I20" s="4" t="s">
+      <c r="I19" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J20" s="4" t="s">
+      <c r="J19" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="K20" s="4" t="s">
+      <c r="K19" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="L20" s="4" t="s">
+      <c r="L19" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="M20" s="4" t="s">
+      <c r="M19" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="N20" s="4" t="s">
+      <c r="N19" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="O20" s="4" t="s">
+      <c r="O19" s="4" t="s">
         <v>2</v>
       </c>
     </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A20" s="13" t="str">
+        <f>+A4</f>
+        <v>RAFAEL BUSTOS</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D20" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="E20" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F20" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="G20" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H20" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I20" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J20" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K20" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L20" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M20" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N20" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="O20" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A21" s="13" t="s">
-        <v>3</v>
+      <c r="A21" s="6" t="str">
+        <f>+A5</f>
+        <v xml:space="preserve">GEISSLEN ERICES </v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D21" s="12">
         <v>0.4375</v>
@@ -1422,28 +1425,20 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N21" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O21" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D22" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="E22" s="12">
-        <v>0.79166666666666663</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
       <c r="F22" s="12">
         <v>0.4375</v>
       </c>
@@ -1469,21 +1464,22 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N22" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O22" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="6" t="s">
-        <v>5</v>
+      <c r="A23" s="6" t="str">
+        <f>+A6</f>
+        <v>LISSETTE MORALES</v>
       </c>
       <c r="B23" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C23" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D23" s="12">
         <v>0.4375</v>
@@ -1516,21 +1512,22 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N23" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O23" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A24" s="6" t="s">
-        <v>6</v>
+      <c r="A24" s="6" t="str">
+        <f>+A7</f>
+        <v xml:space="preserve">CRISTIAN MORALES </v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D24" s="12">
         <v>0.4375</v>
@@ -1563,21 +1560,22 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O24" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
-        <v>7</v>
+      <c r="A25" s="6" t="str">
+        <f>+A8</f>
+        <v>KARIN NAVIA</v>
       </c>
       <c r="B25" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D25" s="12">
         <v>0.4375</v>
@@ -1610,21 +1608,21 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N25" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O25" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B26" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C26" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D26" s="12">
         <v>0.4375</v>
@@ -1657,21 +1655,21 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N26" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O26" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C27" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D27" s="12">
         <v>0.4375</v>
@@ -1704,21 +1702,22 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N27" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O27" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
-        <v>9</v>
+      <c r="A28" s="6" t="str">
+        <f>+A11</f>
+        <v>JORDAN RIMMELIN</v>
       </c>
       <c r="B28" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C28" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D28" s="12">
         <v>0.4375</v>
@@ -1751,21 +1750,21 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N28" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O28" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D29" s="12">
         <v>0.4375</v>
@@ -1798,21 +1797,21 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N29" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O29" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C30" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D30" s="12">
         <v>0.4375</v>
@@ -1845,28 +1844,20 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N30" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O30" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B31" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C31" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D31" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="E31" s="12">
-        <v>0.79166666666666663</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
       <c r="F31" s="12">
         <v>0.4375</v>
       </c>
@@ -1892,21 +1883,21 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N31" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O31" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A32" s="14" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B32" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="D32" s="12">
         <v>0.4375</v>
@@ -1939,15 +1930,15 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N32" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O32" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B35" s="15" t="s">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="C35" s="15"/>
       <c r="D35" s="15"/>
@@ -2042,8 +2033,9 @@
       </c>
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" s="13" t="s">
-        <v>3</v>
+      <c r="A38" s="13" t="str">
+        <f>+A20</f>
+        <v>RAFAEL BUSTOS</v>
       </c>
       <c r="B38" s="10">
         <v>0.4375</v>
@@ -2052,10 +2044,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F38" s="12">
         <v>0.4375</v>
@@ -2082,15 +2074,16 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N38" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O38" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A39" s="6" t="s">
-        <v>4</v>
+      <c r="A39" s="6" t="str">
+        <f>+A21</f>
+        <v xml:space="preserve">GEISSLEN ERICES </v>
       </c>
       <c r="B39" s="12">
         <v>0.4375</v>
@@ -2099,10 +2092,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F39" s="12">
         <v>0.4375</v>
@@ -2129,15 +2122,16 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N39" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O39" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="s">
-        <v>5</v>
+      <c r="A40" s="6" t="str">
+        <f>+A22</f>
+        <v>MAXIMILIANO MEDINA</v>
       </c>
       <c r="B40" s="12">
         <v>0.4375</v>
@@ -2146,10 +2140,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D40" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F40" s="12">
         <v>0.4375</v>
@@ -2176,15 +2170,16 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N40" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O40" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A41" s="6" t="s">
-        <v>6</v>
+      <c r="A41" s="6" t="str">
+        <f>+A23</f>
+        <v>LISSETTE MORALES</v>
       </c>
       <c r="B41" s="12">
         <v>0.4375</v>
@@ -2193,10 +2188,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D41" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F41" s="12">
         <v>0.4375</v>
@@ -2223,15 +2218,16 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N41" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O41" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="s">
-        <v>7</v>
+      <c r="A42" s="6" t="str">
+        <f>+A24</f>
+        <v xml:space="preserve">CRISTIAN MORALES </v>
       </c>
       <c r="B42" s="12">
         <v>0.4375</v>
@@ -2240,10 +2236,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D42" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F42" s="12">
         <v>0.4375</v>
@@ -2270,15 +2266,16 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N42" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O42" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="s">
-        <v>8</v>
+      <c r="A43" s="6" t="str">
+        <f>+A25</f>
+        <v>KARIN NAVIA</v>
       </c>
       <c r="B43" s="12">
         <v>0.4375</v>
@@ -2287,10 +2284,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D43" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F43" s="12">
         <v>0.4375</v>
@@ -2317,15 +2314,15 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N43" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O43" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A44" s="6" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="B44" s="12">
         <v>0.4375</v>
@@ -2334,10 +2331,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D44" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F44" s="12">
         <v>0.4375</v>
@@ -2364,15 +2361,15 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N44" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O44" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B45" s="12">
         <v>0.4375</v>
@@ -2381,10 +2378,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D45" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F45" s="12">
         <v>0.4375</v>
@@ -2411,15 +2408,16 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N45" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O45" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="s">
-        <v>10</v>
+      <c r="A46" s="6" t="str">
+        <f>+A28</f>
+        <v>JORDAN RIMMELIN</v>
       </c>
       <c r="B46" s="12">
         <v>0.4375</v>
@@ -2428,10 +2426,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D46" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F46" s="12">
         <v>0.4375</v>
@@ -2458,15 +2456,15 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O46" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="B47" s="12">
         <v>0.4375</v>
@@ -2475,10 +2473,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D47" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F47" s="12">
         <v>0.4375</v>
@@ -2505,15 +2503,15 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N47" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O47" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B48" s="12">
         <v>0.4375</v>
@@ -2522,10 +2520,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D48" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F48" s="12">
         <v>0.4375</v>
@@ -2552,15 +2550,16 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N48" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O48" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A49" s="14" t="s">
-        <v>18</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A49" s="6" t="str">
+        <f>+A31</f>
+        <v>MATIAS BERENGUELA</v>
       </c>
       <c r="B49" s="12">
         <v>0.4375</v>
@@ -2569,10 +2568,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D49" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F49" s="12">
         <v>0.4375</v>
@@ -2599,158 +2598,159 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N49" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="O49" s="11" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="52" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B52" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="C52" s="15"/>
-      <c r="D52" s="15"/>
-      <c r="E52" s="15"/>
-      <c r="F52" s="15"/>
-      <c r="G52" s="15"/>
-      <c r="H52" s="15"/>
-      <c r="I52" s="15"/>
-      <c r="J52" s="15"/>
-      <c r="K52" s="15"/>
-      <c r="L52" s="15"/>
-      <c r="M52" s="15"/>
-      <c r="N52" s="15"/>
-      <c r="O52" s="15"/>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A50" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B50" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C50" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="G50" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H50" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I50" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J50" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K50" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L50" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M50" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N50" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="O50" s="11" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="53" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="1" t="s">
+      <c r="B53" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="C53" s="15"/>
+      <c r="D53" s="15"/>
+      <c r="E53" s="15"/>
+      <c r="F53" s="15"/>
+      <c r="G53" s="15"/>
+      <c r="H53" s="15"/>
+      <c r="I53" s="15"/>
+      <c r="J53" s="15"/>
+      <c r="K53" s="15"/>
+      <c r="L53" s="15"/>
+      <c r="M53" s="15"/>
+      <c r="N53" s="15"/>
+      <c r="O53" s="15"/>
+    </row>
+    <row r="54" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B53" s="16">
+      <c r="B54" s="16">
         <v>46258</v>
       </c>
-      <c r="C53" s="17"/>
-      <c r="D53" s="16">
+      <c r="C54" s="17"/>
+      <c r="D54" s="16">
         <v>46259</v>
       </c>
-      <c r="E53" s="17"/>
-      <c r="F53" s="16">
+      <c r="E54" s="17"/>
+      <c r="F54" s="16">
         <v>46260</v>
       </c>
-      <c r="G53" s="17"/>
-      <c r="H53" s="16">
+      <c r="G54" s="17"/>
+      <c r="H54" s="16">
         <v>46261</v>
       </c>
-      <c r="I53" s="17"/>
-      <c r="J53" s="16">
+      <c r="I54" s="17"/>
+      <c r="J54" s="16">
         <v>46262</v>
       </c>
-      <c r="K53" s="17"/>
-      <c r="L53" s="16">
+      <c r="K54" s="17"/>
+      <c r="L54" s="16">
         <v>46263</v>
       </c>
-      <c r="M53" s="17"/>
-      <c r="N53" s="16">
+      <c r="M54" s="17"/>
+      <c r="N54" s="16">
         <v>46264</v>
       </c>
-      <c r="O53" s="17"/>
-    </row>
-    <row r="54" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="2"/>
-      <c r="B54" s="7" t="s">
+      <c r="O54" s="17"/>
+    </row>
+    <row r="55" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A55" s="2"/>
+      <c r="B55" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C54" s="7" t="s">
+      <c r="C55" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D54" s="8" t="s">
+      <c r="D55" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E54" s="8" t="s">
+      <c r="E55" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F54" s="8" t="s">
+      <c r="F55" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="G54" s="8" t="s">
+      <c r="G55" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H54" s="8" t="s">
+      <c r="H55" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="I54" s="8" t="s">
+      <c r="I55" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="J54" s="8" t="s">
+      <c r="J55" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="K54" s="8" t="s">
+      <c r="K55" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="L54" s="8" t="s">
+      <c r="L55" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="M54" s="8" t="s">
+      <c r="M55" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="N54" s="8" t="s">
+      <c r="N55" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="O54" s="8" t="s">
+      <c r="O55" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A55" s="13" t="s">
-        <v>3</v>
-      </c>
-      <c r="B55" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C55" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D55" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="E55" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F55" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G55" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H55" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I55" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="J55" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K55" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L55" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M55" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N55" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="O55" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A56" s="6" t="s">
-        <v>4</v>
+      <c r="A56" s="13" t="str">
+        <f>+A38</f>
+        <v>RAFAEL BUSTOS</v>
       </c>
       <c r="B56" s="12">
         <v>0.4375</v>
@@ -2759,22 +2759,22 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D56" s="12">
-        <v>0.41666666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="E56" s="12">
-        <v>0.83333333333333337</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="F56" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J56" s="12">
         <v>0.41666666666666669</v>
@@ -2792,59 +2792,61 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="O56" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A57" s="6" t="str">
+        <f>+A39</f>
+        <v xml:space="preserve">GEISSLEN ERICES </v>
+      </c>
+      <c r="B57" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C57" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D57" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E57" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F57" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G57" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H57" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I57" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J57" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K57" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L57" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M57" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N57" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="O57" s="12">
         <v>0.77083333333333337</v>
       </c>
     </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A57" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B57" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C57" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D57" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="E57" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F57" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G57" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H57" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I57" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="J57" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K57" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L57" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M57" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N57" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="O57" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A58" s="6" t="s">
-        <v>6</v>
+      <c r="A58" s="6" t="str">
+        <f>+A40</f>
+        <v>MAXIMILIANO MEDINA</v>
       </c>
       <c r="B58" s="12">
         <v>0.4375</v>
@@ -2853,22 +2855,22 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D58" s="12">
-        <v>0.41666666666666669</v>
+        <v>0.4375</v>
       </c>
       <c r="E58" s="12">
-        <v>0.83333333333333337</v>
+        <v>0.79166666666666663</v>
       </c>
       <c r="F58" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J58" s="12">
         <v>0.41666666666666669</v>
@@ -2886,59 +2888,61 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="O58" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A59" s="6" t="str">
+        <f>+A41</f>
+        <v>LISSETTE MORALES</v>
+      </c>
+      <c r="B59" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C59" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D59" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E59" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F59" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G59" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I59" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J59" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K59" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L59" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M59" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N59" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="O59" s="12">
         <v>0.77083333333333337</v>
       </c>
     </row>
-    <row r="59" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A59" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="B59" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C59" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D59" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="E59" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F59" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="G59" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="H59" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="I59" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="J59" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K59" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L59" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M59" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N59" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="O59" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A60" s="6" t="s">
-        <v>8</v>
+      <c r="A60" s="6" t="str">
+        <f>+A42</f>
+        <v xml:space="preserve">CRISTIAN MORALES </v>
       </c>
       <c r="B60" s="12">
         <v>0.4375</v>
@@ -2953,16 +2957,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F60" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H60" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I60" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J60" s="12">
         <v>0.41666666666666669</v>
@@ -2984,8 +2988,9 @@
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A61" s="6" t="s">
-        <v>19</v>
+      <c r="A61" s="6" t="str">
+        <f>+A43</f>
+        <v>KARIN NAVIA</v>
       </c>
       <c r="B61" s="12">
         <v>0.4375</v>
@@ -3000,16 +3005,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F61" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H61" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I61" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J61" s="12">
         <v>0.41666666666666669</v>
@@ -3032,7 +3037,7 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B62" s="12">
         <v>0.4375</v>
@@ -3047,16 +3052,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F62" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H62" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I62" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J62" s="12">
         <v>0.41666666666666669</v>
@@ -3079,7 +3084,7 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B63" s="12">
         <v>0.4375</v>
@@ -3094,16 +3099,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F63" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H63" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I63" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J63" s="12">
         <v>0.41666666666666669</v>
@@ -3125,8 +3130,9 @@
       </c>
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A64" s="6" t="s">
-        <v>11</v>
+      <c r="A64" s="6" t="str">
+        <f>+A46</f>
+        <v>JORDAN RIMMELIN</v>
       </c>
       <c r="B64" s="12">
         <v>0.4375</v>
@@ -3141,16 +3147,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J64" s="12">
         <v>0.41666666666666669</v>
@@ -3173,7 +3179,7 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B65" s="12">
         <v>0.4375</v>
@@ -3188,16 +3194,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F65" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H65" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I65" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J65" s="12">
         <v>0.41666666666666669</v>
@@ -3218,9 +3224,9 @@
         <v>0.83333333333333337</v>
       </c>
     </row>
-    <row r="66" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="14" t="s">
-        <v>18</v>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A66" s="6" t="s">
+        <v>5</v>
       </c>
       <c r="B66" s="12">
         <v>0.4375</v>
@@ -3235,16 +3241,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F66" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="G66" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="H66" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="I66" s="11" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="J66" s="12">
         <v>0.41666666666666669</v>
@@ -3262,11 +3268,130 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="O66" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A67" s="6" t="str">
+        <f>+A49</f>
+        <v>MATIAS BERENGUELA</v>
+      </c>
+      <c r="B67" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C67" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D67" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="E67" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F67" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G67" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H67" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I67" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J67" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K67" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L67" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M67" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N67" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="O67" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="14" t="s">
+        <v>11</v>
+      </c>
+      <c r="B68" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C68" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D68" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="E68" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G68" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H68" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I68" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J68" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K68" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L68" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M68" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N68" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="O68" s="12">
         <v>0.83333333333333337</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="B53:O53"/>
+    <mergeCell ref="B54:C54"/>
+    <mergeCell ref="D54:E54"/>
+    <mergeCell ref="F54:G54"/>
+    <mergeCell ref="H54:I54"/>
+    <mergeCell ref="J54:K54"/>
+    <mergeCell ref="L54:M54"/>
+    <mergeCell ref="N54:O54"/>
+    <mergeCell ref="B35:O35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="L36:M36"/>
+    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="B17:O17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="J18:K18"/>
+    <mergeCell ref="L18:M18"/>
+    <mergeCell ref="N18:O18"/>
     <mergeCell ref="B1:O1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
@@ -3275,30 +3400,6 @@
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="N2:O2"/>
-    <mergeCell ref="B18:O18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="J19:K19"/>
-    <mergeCell ref="L19:M19"/>
-    <mergeCell ref="N19:O19"/>
-    <mergeCell ref="B35:O35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="N36:O36"/>
-    <mergeCell ref="B52:O52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="N53:O53"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/horarios.xlsx
+++ b/horarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dreame\Desktop\Claude\Dreame\Turnos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F71C0268-9425-466C-A616-8870E8896F72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92B3F74F-28B6-416A-91B8-151C21437A34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="288" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="22">
   <si>
     <t>Promotor</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>MATIAS BERENGUELA</t>
+  </si>
+  <si>
+    <t>DIEGO MARTINEZ</t>
   </si>
 </sst>
 </file>
@@ -604,7 +607,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DB7FB46-34C8-4ECD-A089-0D01F6EF7C8B}">
-  <dimension ref="A1:R68"/>
+  <dimension ref="A1:R71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.33203125" bestFit="1" customWidth="1"/>
@@ -1889,441 +1892,433 @@
         <v>10</v>
       </c>
     </row>
-    <row r="32" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A32" s="14" t="s">
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="G32" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H32" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I32" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J32" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K32" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L32" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M32" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N32" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="O32" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A33" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B32" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="D32" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="E32" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F32" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="G32" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H32" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="I32" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J32" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K32" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L32" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M32" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N32" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="O32" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B35" s="15" t="s">
+      <c r="B33" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="D33" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="E33" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F33" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="G33" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H33" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I33" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J33" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K33" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L33" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M33" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N33" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="O33" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="C35" s="15"/>
-      <c r="D35" s="15"/>
-      <c r="E35" s="15"/>
-      <c r="F35" s="15"/>
-      <c r="G35" s="15"/>
-      <c r="H35" s="15"/>
-      <c r="I35" s="15"/>
-      <c r="J35" s="15"/>
-      <c r="K35" s="15"/>
-      <c r="L35" s="15"/>
-      <c r="M35" s="15"/>
-      <c r="N35" s="15"/>
-      <c r="O35" s="15"/>
-    </row>
-    <row r="36" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="1" t="s">
+      <c r="C36" s="15"/>
+      <c r="D36" s="15"/>
+      <c r="E36" s="15"/>
+      <c r="F36" s="15"/>
+      <c r="G36" s="15"/>
+      <c r="H36" s="15"/>
+      <c r="I36" s="15"/>
+      <c r="J36" s="15"/>
+      <c r="K36" s="15"/>
+      <c r="L36" s="15"/>
+      <c r="M36" s="15"/>
+      <c r="N36" s="15"/>
+      <c r="O36" s="15"/>
+    </row>
+    <row r="37" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B36" s="16">
+      <c r="B37" s="16">
         <v>46251</v>
       </c>
-      <c r="C36" s="17"/>
-      <c r="D36" s="16">
+      <c r="C37" s="17"/>
+      <c r="D37" s="16">
         <v>46252</v>
       </c>
-      <c r="E36" s="17"/>
-      <c r="F36" s="16">
+      <c r="E37" s="17"/>
+      <c r="F37" s="16">
         <v>46253</v>
       </c>
-      <c r="G36" s="17"/>
-      <c r="H36" s="16">
+      <c r="G37" s="17"/>
+      <c r="H37" s="16">
         <v>46254</v>
       </c>
-      <c r="I36" s="17"/>
-      <c r="J36" s="16">
+      <c r="I37" s="17"/>
+      <c r="J37" s="16">
         <v>46255</v>
       </c>
-      <c r="K36" s="17"/>
-      <c r="L36" s="16">
+      <c r="K37" s="17"/>
+      <c r="L37" s="16">
         <v>46256</v>
       </c>
-      <c r="M36" s="17"/>
-      <c r="N36" s="16">
+      <c r="M37" s="17"/>
+      <c r="N37" s="16">
         <v>46257</v>
       </c>
-      <c r="O36" s="17"/>
-    </row>
-    <row r="37" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="2"/>
-      <c r="B37" s="7" t="s">
+      <c r="O37" s="17"/>
+    </row>
+    <row r="38" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A38" s="2"/>
+      <c r="B38" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C37" s="7" t="s">
+      <c r="C38" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D37" s="8" t="s">
+      <c r="D38" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E37" s="4" t="s">
+      <c r="E38" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="F38" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G37" s="4" t="s">
+      <c r="G38" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H37" s="4" t="s">
+      <c r="H38" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="I37" s="4" t="s">
+      <c r="I38" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J37" s="4" t="s">
+      <c r="J38" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="K37" s="4" t="s">
+      <c r="K38" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="L37" s="4" t="s">
+      <c r="L38" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="M37" s="4" t="s">
+      <c r="M38" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="N37" s="4" t="s">
+      <c r="N38" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="O37" s="4" t="s">
+      <c r="O38" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A38" s="13" t="str">
+    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A39" s="13" t="str">
         <f>+A20</f>
         <v>RAFAEL BUSTOS</v>
       </c>
-      <c r="B38" s="10">
-        <v>0.4375</v>
-      </c>
-      <c r="C38" s="10">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D38" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="E38" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F38" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="G38" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H38" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="I38" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J38" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K38" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L38" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M38" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N38" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="O38" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="39" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A39" s="6" t="str">
+      <c r="B39" s="10">
+        <v>0.4375</v>
+      </c>
+      <c r="C39" s="10">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D39" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="E39" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F39" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="G39" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H39" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I39" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J39" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K39" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L39" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M39" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N39" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="O39" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A40" s="6" t="str">
         <f>+A21</f>
         <v xml:space="preserve">GEISSLEN ERICES </v>
       </c>
-      <c r="B39" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C39" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D39" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E39" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F39" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="G39" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H39" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="I39" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J39" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K39" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L39" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M39" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N39" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="O39" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A40" s="6" t="str">
+      <c r="B40" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C40" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D40" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E40" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F40" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="G40" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H40" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I40" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J40" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K40" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L40" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M40" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N40" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="O40" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A41" s="6" t="str">
         <f>+A22</f>
         <v>MAXIMILIANO MEDINA</v>
       </c>
-      <c r="B40" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C40" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D40" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E40" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F40" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="G40" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H40" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="I40" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J40" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K40" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L40" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M40" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N40" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="O40" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A41" s="6" t="str">
+      <c r="B41" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C41" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D41" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E41" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F41" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="G41" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H41" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I41" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J41" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K41" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L41" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M41" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N41" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="O41" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A42" s="6" t="str">
         <f>+A23</f>
         <v>LISSETTE MORALES</v>
       </c>
-      <c r="B41" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C41" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D41" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E41" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F41" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="G41" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H41" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="I41" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J41" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K41" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L41" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M41" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N41" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="O41" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A42" s="6" t="str">
+      <c r="B42" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C42" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F42" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="G42" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H42" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I42" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J42" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K42" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L42" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M42" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N42" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="O42" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A43" s="6" t="str">
         <f>+A24</f>
         <v xml:space="preserve">CRISTIAN MORALES </v>
       </c>
-      <c r="B42" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C42" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D42" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E42" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F42" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="G42" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H42" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="I42" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J42" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K42" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L42" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M42" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N42" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="O42" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="43" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A43" s="6" t="str">
+      <c r="B43" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C43" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E43" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F43" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="G43" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H43" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I43" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J43" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K43" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L43" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M43" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N43" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="O43" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A44" s="6" t="str">
         <f>+A25</f>
         <v>KARIN NAVIA</v>
       </c>
-      <c r="B43" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C43" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D43" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E43" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F43" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="G43" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H43" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="I43" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J43" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K43" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L43" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M43" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N43" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="O43" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="44" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A44" s="6" t="s">
-        <v>12</v>
-      </c>
       <c r="B44" s="12">
         <v>0.4375</v>
       </c>
@@ -2369,103 +2364,103 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B45" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C45" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E45" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F45" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="G45" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H45" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I45" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J45" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K45" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L45" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M45" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N45" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="O45" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A46" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B45" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C45" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E45" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F45" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="G45" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H45" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="I45" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J45" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K45" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L45" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M45" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N45" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="O45" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A46" s="6" t="str">
+      <c r="B46" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C46" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E46" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F46" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="G46" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H46" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I46" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J46" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K46" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L46" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M46" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N46" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="O46" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A47" s="6" t="str">
         <f>+A28</f>
         <v>JORDAN RIMMELIN</v>
       </c>
-      <c r="B46" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C46" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E46" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F46" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="G46" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H46" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="I46" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J46" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K46" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L46" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M46" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N46" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="O46" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="s">
-        <v>4</v>
-      </c>
       <c r="B47" s="12">
         <v>0.4375</v>
       </c>
@@ -2511,342 +2506,341 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B48" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C48" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D48" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E48" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F48" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="G48" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H48" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I48" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J48" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K48" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L48" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M48" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N48" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="O48" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A49" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B48" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C48" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D48" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E48" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F48" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="G48" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H48" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="I48" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J48" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K48" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L48" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M48" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N48" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="O48" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A49" s="6" t="str">
+      <c r="B49" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C49" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D49" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E49" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F49" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="G49" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H49" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I49" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J49" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K49" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L49" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M49" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N49" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="O49" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A50" s="6" t="str">
         <f>+A31</f>
         <v>MATIAS BERENGUELA</v>
       </c>
-      <c r="B49" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C49" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D49" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E49" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F49" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="G49" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H49" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="I49" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J49" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K49" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L49" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M49" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N49" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="O49" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="50" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A50" s="14" t="s">
+      <c r="B50" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C50" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D50" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E50" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F50" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="G50" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H50" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I50" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J50" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K50" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L50" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M50" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N50" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="O50" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A51" s="6" t="str">
+        <f>+A32</f>
+        <v>DIEGO MARTINEZ</v>
+      </c>
+      <c r="B51" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C51" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D51" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E51" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F51" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="G51" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H51" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I51" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J51" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K51" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L51" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M51" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N51" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="O51" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B50" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C50" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D50" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="E50" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F50" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="G50" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H50" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="I50" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="J50" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K50" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L50" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M50" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N50" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="O50" s="11" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="53" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B53" s="15" t="s">
+      <c r="B52" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C52" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D52" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="E52" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F52" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="G52" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H52" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="I52" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="J52" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K52" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L52" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M52" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N52" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="O52" s="11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B55" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="C53" s="15"/>
-      <c r="D53" s="15"/>
-      <c r="E53" s="15"/>
-      <c r="F53" s="15"/>
-      <c r="G53" s="15"/>
-      <c r="H53" s="15"/>
-      <c r="I53" s="15"/>
-      <c r="J53" s="15"/>
-      <c r="K53" s="15"/>
-      <c r="L53" s="15"/>
-      <c r="M53" s="15"/>
-      <c r="N53" s="15"/>
-      <c r="O53" s="15"/>
-    </row>
-    <row r="54" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="1" t="s">
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="15"/>
+      <c r="F55" s="15"/>
+      <c r="G55" s="15"/>
+      <c r="H55" s="15"/>
+      <c r="I55" s="15"/>
+      <c r="J55" s="15"/>
+      <c r="K55" s="15"/>
+      <c r="L55" s="15"/>
+      <c r="M55" s="15"/>
+      <c r="N55" s="15"/>
+      <c r="O55" s="15"/>
+    </row>
+    <row r="56" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B54" s="16">
+      <c r="B56" s="16">
         <v>46258</v>
       </c>
-      <c r="C54" s="17"/>
-      <c r="D54" s="16">
+      <c r="C56" s="17"/>
+      <c r="D56" s="16">
         <v>46259</v>
       </c>
-      <c r="E54" s="17"/>
-      <c r="F54" s="16">
+      <c r="E56" s="17"/>
+      <c r="F56" s="16">
         <v>46260</v>
       </c>
-      <c r="G54" s="17"/>
-      <c r="H54" s="16">
+      <c r="G56" s="17"/>
+      <c r="H56" s="16">
         <v>46261</v>
       </c>
-      <c r="I54" s="17"/>
-      <c r="J54" s="16">
+      <c r="I56" s="17"/>
+      <c r="J56" s="16">
         <v>46262</v>
       </c>
-      <c r="K54" s="17"/>
-      <c r="L54" s="16">
+      <c r="K56" s="17"/>
+      <c r="L56" s="16">
         <v>46263</v>
       </c>
-      <c r="M54" s="17"/>
-      <c r="N54" s="16">
+      <c r="M56" s="17"/>
+      <c r="N56" s="16">
         <v>46264</v>
       </c>
-      <c r="O54" s="17"/>
-    </row>
-    <row r="55" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="2"/>
-      <c r="B55" s="7" t="s">
+      <c r="O56" s="17"/>
+    </row>
+    <row r="57" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="2"/>
+      <c r="B57" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C55" s="7" t="s">
+      <c r="C57" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D55" s="8" t="s">
+      <c r="D57" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E55" s="8" t="s">
+      <c r="E57" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F55" s="8" t="s">
+      <c r="F57" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="G55" s="8" t="s">
+      <c r="G57" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H55" s="8" t="s">
+      <c r="H57" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="I55" s="8" t="s">
+      <c r="I57" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="J55" s="8" t="s">
+      <c r="J57" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="K55" s="8" t="s">
+      <c r="K57" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="L55" s="8" t="s">
+      <c r="L57" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="M55" s="8" t="s">
+      <c r="M57" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="N55" s="8" t="s">
+      <c r="N57" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="O55" s="8" t="s">
+      <c r="O57" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A56" s="13" t="str">
-        <f>+A38</f>
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A58" s="13" t="str">
+        <f t="shared" ref="A58:A63" si="0">+A39</f>
         <v>RAFAEL BUSTOS</v>
-      </c>
-      <c r="B56" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C56" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D56" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="E56" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F56" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G56" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H56" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I56" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J56" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K56" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L56" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M56" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N56" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="O56" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="57" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A57" s="6" t="str">
-        <f>+A39</f>
-        <v xml:space="preserve">GEISSLEN ERICES </v>
-      </c>
-      <c r="B57" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C57" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D57" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="E57" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="F57" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G57" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H57" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I57" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J57" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K57" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L57" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M57" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N57" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="O57" s="12">
-        <v>0.77083333333333337</v>
-      </c>
-    </row>
-    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A58" s="6" t="str">
-        <f>+A40</f>
-        <v>MAXIMILIANO MEDINA</v>
       </c>
       <c r="B58" s="12">
         <v>0.4375</v>
@@ -2893,8 +2887,8 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="str">
-        <f>+A41</f>
-        <v>LISSETTE MORALES</v>
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">GEISSLEN ERICES </v>
       </c>
       <c r="B59" s="12">
         <v>0.4375</v>
@@ -2941,8 +2935,8 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="str">
-        <f>+A42</f>
-        <v xml:space="preserve">CRISTIAN MORALES </v>
+        <f t="shared" si="0"/>
+        <v>MAXIMILIANO MEDINA</v>
       </c>
       <c r="B60" s="12">
         <v>0.4375</v>
@@ -2989,150 +2983,151 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A61" s="6" t="str">
-        <f>+A43</f>
+        <f t="shared" si="0"/>
+        <v>LISSETTE MORALES</v>
+      </c>
+      <c r="B61" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C61" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D61" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="E61" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="F61" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G61" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H61" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I61" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J61" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K61" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L61" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M61" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N61" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="O61" s="12">
+        <v>0.77083333333333337</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A62" s="6" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">CRISTIAN MORALES </v>
+      </c>
+      <c r="B62" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C62" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D62" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="E62" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F62" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G62" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H62" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I62" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J62" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K62" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L62" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M62" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N62" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="O62" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A63" s="6" t="str">
+        <f t="shared" si="0"/>
         <v>KARIN NAVIA</v>
       </c>
-      <c r="B61" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C61" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D61" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="E61" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F61" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G61" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H61" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I61" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J61" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K61" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L61" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M61" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N61" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="O61" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="62" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A62" s="6" t="s">
+      <c r="B63" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C63" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D63" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="E63" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F63" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G63" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H63" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I63" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J63" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K63" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L63" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M63" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N63" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="O63" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A64" s="6" t="s">
         <v>12</v>
-      </c>
-      <c r="B62" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C62" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D62" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="E62" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F62" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G62" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H62" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I62" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J62" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K62" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L62" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M62" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N62" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="O62" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A63" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B63" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C63" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D63" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="E63" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F63" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G63" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H63" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I63" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J63" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K63" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L63" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M63" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N63" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="O63" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="64" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A64" s="6" t="str">
-        <f>+A46</f>
-        <v>JORDAN RIMMELIN</v>
       </c>
       <c r="B64" s="12">
         <v>0.4375</v>
@@ -3179,211 +3174,346 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="B65" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C65" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D65" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="E65" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F65" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G65" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H65" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I65" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J65" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K65" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L65" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M65" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N65" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="O65" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A66" s="6" t="str">
+        <f>+A47</f>
+        <v>JORDAN RIMMELIN</v>
+      </c>
+      <c r="B66" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C66" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D66" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="E66" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F66" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G66" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H66" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I66" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J66" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K66" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L66" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M66" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N66" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="O66" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A67" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="B65" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C65" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D65" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="E65" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F65" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G65" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H65" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I65" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J65" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K65" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L65" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M65" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N65" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="O65" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="66" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A66" s="6" t="s">
+      <c r="B67" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C67" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D67" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="E67" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F67" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G67" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H67" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I67" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J67" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K67" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L67" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M67" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N67" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="O67" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A68" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B66" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C66" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D66" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="E66" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F66" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G66" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H66" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I66" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J66" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K66" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L66" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M66" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N66" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="O66" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="67" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A67" s="6" t="str">
-        <f>+A49</f>
+      <c r="B68" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C68" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D68" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="E68" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F68" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G68" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H68" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I68" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J68" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K68" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L68" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M68" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N68" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="O68" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A69" s="6" t="str">
+        <f>+A50</f>
         <v>MATIAS BERENGUELA</v>
       </c>
-      <c r="B67" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C67" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D67" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="E67" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F67" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G67" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H67" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I67" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J67" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K67" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L67" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M67" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N67" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="O67" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-    </row>
-    <row r="68" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="14" t="s">
+      <c r="B69" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C69" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D69" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="E69" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F69" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G69" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H69" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I69" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J69" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K69" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L69" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M69" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N69" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="O69" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A70" s="6" t="str">
+        <f>+A51</f>
+        <v>DIEGO MARTINEZ</v>
+      </c>
+      <c r="B70" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C70" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D70" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="E70" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F70" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G70" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H70" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I70" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J70" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K70" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L70" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M70" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N70" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="O70" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+    </row>
+    <row r="71" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="B68" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="C68" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D68" s="12">
-        <v>0.4375</v>
-      </c>
-      <c r="E68" s="12">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F68" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G68" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="H68" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="I68" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="J68" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="K68" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="L68" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="M68" s="12">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N68" s="12">
-        <v>0.41666666666666669</v>
-      </c>
-      <c r="O68" s="12">
+      <c r="B71" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="C71" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D71" s="12">
+        <v>0.4375</v>
+      </c>
+      <c r="E71" s="12">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F71" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="G71" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="H71" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="I71" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="J71" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="K71" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="L71" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="M71" s="12">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N71" s="12">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="O71" s="12">
         <v>0.83333333333333337</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="B53:O53"/>
-    <mergeCell ref="B54:C54"/>
-    <mergeCell ref="D54:E54"/>
-    <mergeCell ref="F54:G54"/>
-    <mergeCell ref="H54:I54"/>
-    <mergeCell ref="J54:K54"/>
-    <mergeCell ref="L54:M54"/>
-    <mergeCell ref="N54:O54"/>
-    <mergeCell ref="B35:O35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="N36:O36"/>
+    <mergeCell ref="B1:O1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+    <mergeCell ref="N2:O2"/>
     <mergeCell ref="B17:O17"/>
     <mergeCell ref="B18:C18"/>
     <mergeCell ref="D18:E18"/>
@@ -3392,14 +3522,22 @@
     <mergeCell ref="J18:K18"/>
     <mergeCell ref="L18:M18"/>
     <mergeCell ref="N18:O18"/>
-    <mergeCell ref="B1:O1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="L2:M2"/>
-    <mergeCell ref="N2:O2"/>
+    <mergeCell ref="B36:O36"/>
+    <mergeCell ref="B37:C37"/>
+    <mergeCell ref="D37:E37"/>
+    <mergeCell ref="F37:G37"/>
+    <mergeCell ref="H37:I37"/>
+    <mergeCell ref="J37:K37"/>
+    <mergeCell ref="L37:M37"/>
+    <mergeCell ref="N37:O37"/>
+    <mergeCell ref="B55:O55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="N56:O56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/horarios.xlsx
+++ b/horarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dreame\Desktop\Claude\Dreame\Turnos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85B1FC60-D1C5-459A-8C24-305877D83683}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F748EE-CEBD-4246-A31F-C935336E39EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="25">
   <si>
     <t>Promotor</t>
   </si>
@@ -108,6 +108,9 @@
   </si>
   <si>
     <t>Feriado</t>
+  </si>
+  <si>
+    <t>CAROLINA PEDREROS</t>
   </si>
 </sst>
 </file>
@@ -675,7 +678,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DB7FB46-34C8-4ECD-A089-0D01F6EF7C8B}">
-  <dimension ref="A1:R103"/>
+  <dimension ref="A1:R104"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="34.33203125" bestFit="1" customWidth="1"/>
@@ -1358,439 +1361,439 @@
       </c>
     </row>
     <row r="16" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="18" t="s">
+      <c r="A16" s="17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16" s="19">
+        <v>0.4375</v>
+      </c>
+      <c r="C16" s="19">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D16" s="19">
+        <v>0.4375</v>
+      </c>
+      <c r="E16" s="19">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F16" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G16" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="I16" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="J16" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="K16" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L16" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="M16" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N16" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="O16" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="B16" s="19">
-        <v>0.4375</v>
-      </c>
-      <c r="C16" s="19">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D16" s="19">
-        <v>0.4375</v>
-      </c>
-      <c r="E16" s="19">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="G16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="H16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="I16" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="J16" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="K16" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L16" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="M16" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N16" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="O16" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B20" s="14" t="s">
+      <c r="B17" s="19">
+        <v>0.4375</v>
+      </c>
+      <c r="C17" s="19">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D17" s="19">
+        <v>0.4375</v>
+      </c>
+      <c r="E17" s="19">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F17" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G17" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="H17" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="I17" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="J17" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="K17" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L17" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="M17" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N17" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="O17" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B21" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
-      <c r="L20" s="14"/>
-      <c r="M20" s="14"/>
-      <c r="N20" s="14"/>
-      <c r="O20" s="14"/>
-    </row>
-    <row r="21" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="1" t="s">
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+    </row>
+    <row r="22" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B22" s="15">
         <v>46272</v>
       </c>
-      <c r="C21" s="16"/>
-      <c r="D21" s="15">
+      <c r="C22" s="16"/>
+      <c r="D22" s="15">
         <v>46273</v>
       </c>
-      <c r="E21" s="16"/>
-      <c r="F21" s="15">
+      <c r="E22" s="16"/>
+      <c r="F22" s="15">
         <v>46274</v>
       </c>
-      <c r="G21" s="16"/>
-      <c r="H21" s="15">
+      <c r="G22" s="16"/>
+      <c r="H22" s="15">
         <v>46275</v>
       </c>
-      <c r="I21" s="16"/>
-      <c r="J21" s="15">
+      <c r="I22" s="16"/>
+      <c r="J22" s="15">
         <v>46276</v>
       </c>
-      <c r="K21" s="16"/>
-      <c r="L21" s="15">
+      <c r="K22" s="16"/>
+      <c r="L22" s="15">
         <v>46277</v>
       </c>
-      <c r="M21" s="16"/>
-      <c r="N21" s="15">
+      <c r="M22" s="16"/>
+      <c r="N22" s="15">
         <v>46278</v>
       </c>
-      <c r="O21" s="16"/>
-    </row>
-    <row r="22" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="2"/>
-      <c r="B22" s="4" t="s">
+      <c r="O22" s="16"/>
+    </row>
+    <row r="23" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="2"/>
+      <c r="B23" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D23" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F23" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G22" s="4" t="s">
+      <c r="G23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H22" s="4" t="s">
+      <c r="H23" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="I22" s="4" t="s">
+      <c r="I23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J22" s="4" t="s">
+      <c r="J23" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="K22" s="4" t="s">
+      <c r="K23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="L22" s="4" t="s">
+      <c r="L23" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="M22" s="4" t="s">
+      <c r="M23" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="N22" s="4" t="s">
+      <c r="N23" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="O22" s="4" t="s">
+      <c r="O23" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A23" s="12" t="str">
+    <row r="24" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A24" s="12" t="str">
         <f>+A4</f>
         <v>RAFAEL BUSTOS</v>
       </c>
-      <c r="B23" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="C23" s="21">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D23" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F23" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="G23" s="21">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H23" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="I23" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="J23" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="K23" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L23" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="M23" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N23" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O23" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="20" t="str">
+      <c r="B24" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="C24" s="21">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F24" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="G24" s="21">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H24" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="I24" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="J24" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="K24" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L24" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="M24" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N24" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O24" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="20" t="str">
         <f>+A5</f>
         <v xml:space="preserve">GEISSLEN ERICES </v>
       </c>
-      <c r="B24" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="C24" s="21">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D24" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F24" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="G24" s="21">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H24" s="21">
+      <c r="B25" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="C25" s="21">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F25" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="G25" s="21">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H25" s="21">
         <v>0.41666666666666669</v>
       </c>
-      <c r="I24" s="21">
+      <c r="I25" s="21">
         <v>0.83333333333333337</v>
       </c>
-      <c r="J24" s="21">
+      <c r="J25" s="21">
         <v>0.41666666666666669</v>
       </c>
-      <c r="K24" s="21">
+      <c r="K25" s="21">
         <v>0.83333333333333337</v>
       </c>
-      <c r="L24" s="21">
+      <c r="L25" s="21">
         <v>0.41666666666666669</v>
       </c>
-      <c r="M24" s="21">
+      <c r="M25" s="21">
         <v>0.83333333333333337</v>
       </c>
-      <c r="N24" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O24" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A25" s="6" t="s">
+      <c r="N25" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O25" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A26" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B25" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="C25" s="21">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D25" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E25" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F25" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="G25" s="21">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H25" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="I25" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="J25" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="K25" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L25" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="M25" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N25" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O25" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="20" t="str">
+      <c r="B26" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="C26" s="21">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D26" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E26" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F26" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="G26" s="21">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H26" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="I26" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="J26" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="K26" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L26" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="M26" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N26" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O26" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="20" t="str">
         <f>+A6</f>
         <v>LISSETTE MORALES</v>
       </c>
-      <c r="B26" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="C26" s="21">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D26" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E26" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F26" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="G26" s="21">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H26" s="21">
+      <c r="B27" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="C27" s="21">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D27" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E27" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F27" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="G27" s="21">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H27" s="21">
         <v>0.41666666666666669</v>
       </c>
-      <c r="I26" s="21">
+      <c r="I27" s="21">
         <v>0.83333333333333337</v>
       </c>
-      <c r="J26" s="21">
+      <c r="J27" s="21">
         <v>0.41666666666666669</v>
       </c>
-      <c r="K26" s="21">
+      <c r="K27" s="21">
         <v>0.83333333333333337</v>
       </c>
-      <c r="L26" s="21">
+      <c r="L27" s="21">
         <v>0.41666666666666669</v>
       </c>
-      <c r="M26" s="21">
+      <c r="M27" s="21">
         <v>0.83333333333333337</v>
       </c>
-      <c r="N26" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O26" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A27" s="6" t="str">
+      <c r="N27" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O27" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="str">
         <f>+A7</f>
         <v xml:space="preserve">CRISTIAN MORALES </v>
       </c>
-      <c r="B27" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="C27" s="21">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D27" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E27" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="G27" s="21">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H27" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="I27" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="J27" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="K27" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L27" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="M27" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N27" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O27" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="str">
+      <c r="B28" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="C28" s="21">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D28" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E28" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F28" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="G28" s="21">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H28" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="I28" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="J28" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="K28" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L28" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="M28" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N28" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O28" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A29" s="6" t="str">
         <f>+A8</f>
         <v>DIEGO MARTINEZ</v>
       </c>
-      <c r="B28" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="C28" s="21">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D28" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E28" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F28" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="G28" s="21">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H28" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="I28" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="J28" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="K28" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L28" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="M28" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N28" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O28" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A29" s="6" t="s">
-        <v>8</v>
-      </c>
       <c r="B29" s="21">
         <v>0.4375</v>
       </c>
@@ -1836,7 +1839,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B30" s="21">
         <v>0.4375</v>
@@ -1882,139 +1885,139 @@
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A31" s="6" t="str">
+      <c r="A31" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B31" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="C31" s="21">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D31" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E31" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F31" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="G31" s="21">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H31" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="I31" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="J31" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="K31" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L31" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="M31" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N31" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O31" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A32" s="6" t="str">
         <f>+A11</f>
         <v>JORDAN RIMMELIN</v>
       </c>
-      <c r="B31" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="C31" s="21">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D31" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E31" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F31" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="G31" s="21">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H31" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="I31" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="J31" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="K31" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L31" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="M31" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N31" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O31" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="20" t="s">
+      <c r="B32" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="C32" s="21">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D32" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E32" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F32" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="G32" s="21">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H32" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="I32" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="J32" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="K32" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L32" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="M32" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N32" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O32" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B32" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="C32" s="21">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D32" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E32" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F32" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="G32" s="21">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H32" s="21">
+      <c r="B33" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="C33" s="21">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D33" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E33" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F33" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="G33" s="21">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H33" s="21">
         <v>0.41666666666666669</v>
       </c>
-      <c r="I32" s="21">
+      <c r="I33" s="21">
         <v>0.83333333333333337</v>
       </c>
-      <c r="J32" s="21">
+      <c r="J33" s="21">
         <v>0.41666666666666669</v>
       </c>
-      <c r="K32" s="21">
+      <c r="K33" s="21">
         <v>0.83333333333333337</v>
       </c>
-      <c r="L32" s="21">
+      <c r="L33" s="21">
         <v>0.41666666666666669</v>
       </c>
-      <c r="M32" s="21">
+      <c r="M33" s="21">
         <v>0.83333333333333337</v>
-      </c>
-      <c r="N32" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O32" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A33" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="C33" s="21">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D33" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E33" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F33" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="G33" s="21">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H33" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="I33" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="J33" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="K33" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L33" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="M33" s="11">
-        <v>0.85416666666666663</v>
       </c>
       <c r="N33" s="11" t="s">
         <v>6</v>
@@ -2025,7 +2028,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="B34" s="21">
         <v>0.4375</v>
@@ -2072,7 +2075,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B35" s="21">
         <v>0.4375</v>
@@ -2117,345 +2120,345 @@
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="13" t="s">
+    <row r="36" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A36" s="6" t="str">
+        <f>+A16</f>
+        <v>CAROLINA PEDREROS</v>
+      </c>
+      <c r="B36" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="C36" s="21">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D36" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E36" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F36" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="G36" s="21">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H36" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="I36" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="J36" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="K36" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L36" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="M36" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N36" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O36" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A37" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B36" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="C36" s="21">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D36" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="E36" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="F36" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="G36" s="21">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H36" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="I36" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="J36" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="K36" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L36" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="M36" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N36" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O36" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="42" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B42" s="14" t="s">
+      <c r="B37" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="C37" s="21">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D37" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="E37" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="F37" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="G37" s="21">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H37" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="I37" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="J37" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="K37" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L37" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="M37" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N37" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O37" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B43" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-      <c r="G42" s="14"/>
-      <c r="H42" s="14"/>
-      <c r="I42" s="14"/>
-      <c r="J42" s="14"/>
-      <c r="K42" s="14"/>
-      <c r="L42" s="14"/>
-      <c r="M42" s="14"/>
-      <c r="N42" s="14"/>
-      <c r="O42" s="14"/>
-    </row>
-    <row r="43" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A43" s="1" t="s">
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="14"/>
+      <c r="K43" s="14"/>
+      <c r="L43" s="14"/>
+      <c r="M43" s="14"/>
+      <c r="N43" s="14"/>
+      <c r="O43" s="14"/>
+    </row>
+    <row r="44" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A44" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B43" s="15">
+      <c r="B44" s="15">
         <v>46279</v>
       </c>
-      <c r="C43" s="16"/>
-      <c r="D43" s="15">
+      <c r="C44" s="16"/>
+      <c r="D44" s="15">
         <v>46280</v>
       </c>
-      <c r="E43" s="16"/>
-      <c r="F43" s="15">
+      <c r="E44" s="16"/>
+      <c r="F44" s="15">
         <v>46281</v>
       </c>
-      <c r="G43" s="16"/>
-      <c r="H43" s="15">
+      <c r="G44" s="16"/>
+      <c r="H44" s="15">
         <v>46282</v>
       </c>
-      <c r="I43" s="16"/>
-      <c r="J43" s="15">
+      <c r="I44" s="16"/>
+      <c r="J44" s="15">
         <v>46283</v>
       </c>
-      <c r="K43" s="16"/>
-      <c r="L43" s="15">
+      <c r="K44" s="16"/>
+      <c r="L44" s="15">
         <v>46284</v>
       </c>
-      <c r="M43" s="16"/>
-      <c r="N43" s="15">
+      <c r="M44" s="16"/>
+      <c r="N44" s="15">
         <v>46285</v>
       </c>
-      <c r="O43" s="16"/>
-    </row>
-    <row r="44" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="2"/>
-      <c r="B44" s="7" t="s">
+      <c r="O44" s="16"/>
+    </row>
+    <row r="45" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="2"/>
+      <c r="B45" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C44" s="7" t="s">
+      <c r="C45" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D44" s="8" t="s">
+      <c r="D45" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E44" s="4" t="s">
+      <c r="E45" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="F45" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G44" s="4" t="s">
+      <c r="G45" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="H44" s="4" t="s">
+      <c r="H45" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="I44" s="4" t="s">
+      <c r="I45" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="J44" s="4" t="s">
+      <c r="J45" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="K44" s="4" t="s">
+      <c r="K45" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="L44" s="4" t="s">
+      <c r="L45" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="M44" s="4" t="s">
+      <c r="M45" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="N44" s="4" t="s">
+      <c r="N45" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="O44" s="4" t="s">
+      <c r="O45" s="4" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A45" s="12" t="str">
-        <f t="shared" ref="A45:A50" si="0">+A23</f>
+    <row r="46" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A46" s="12" t="str">
+        <f t="shared" ref="A46:A51" si="0">+A24</f>
         <v>RAFAEL BUSTOS</v>
       </c>
-      <c r="B45" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C45" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="D45" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="E45" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F45" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="G45" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H45" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="I45" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="J45" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K45" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="L45" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M45" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="N45" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O45" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="46" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="20" t="str">
+      <c r="B46" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C46" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D46" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="E46" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F46" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="G46" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H46" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I46" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="J46" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="K46" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="M46" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="N46" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O46" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="20" t="str">
         <f t="shared" si="0"/>
         <v xml:space="preserve">GEISSLEN ERICES </v>
       </c>
-      <c r="B46" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C46" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="D46" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="E46" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F46" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="G46" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H46" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="I46" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="J46" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K46" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="L46" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M46" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="N46" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O46" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="47" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A47" s="6" t="str">
+      <c r="B47" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C47" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D47" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="E47" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F47" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="G47" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H47" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I47" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="J47" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="K47" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="M47" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="N47" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O47" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A48" s="6" t="str">
         <f t="shared" si="0"/>
         <v>MAXIMILIANO MEDINA</v>
       </c>
-      <c r="B47" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C47" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="D47" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="E47" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F47" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="G47" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H47" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="I47" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="J47" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K47" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="L47" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M47" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="N47" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O47" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="20" t="str">
+      <c r="B48" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C48" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D48" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="E48" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F48" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="G48" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H48" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I48" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="J48" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="K48" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="M48" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="N48" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O48" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="20" t="str">
         <f t="shared" si="0"/>
         <v>LISSETTE MORALES</v>
-      </c>
-      <c r="B48" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C48" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="D48" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="E48" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F48" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="G48" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H48" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="I48" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="J48" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K48" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="L48" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M48" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="N48" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O48" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="49" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A49" s="6" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">CRISTIAN MORALES </v>
       </c>
       <c r="B49" s="11">
         <v>0.4375</v>
@@ -2503,54 +2506,55 @@
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="str">
         <f t="shared" si="0"/>
+        <v xml:space="preserve">CRISTIAN MORALES </v>
+      </c>
+      <c r="B50" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C50" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D50" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="E50" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F50" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="G50" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H50" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I50" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="J50" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="K50" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="M50" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="N50" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O50" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A51" s="6" t="str">
+        <f t="shared" si="0"/>
         <v>DIEGO MARTINEZ</v>
-      </c>
-      <c r="B50" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C50" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="D50" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="E50" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F50" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="G50" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H50" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="I50" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="J50" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K50" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="L50" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M50" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="N50" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O50" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="51" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A51" s="6" t="s">
-        <v>8</v>
       </c>
       <c r="B51" s="11">
         <v>0.4375</v>
@@ -2597,7 +2601,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B52" s="11">
         <v>0.4375</v>
@@ -2643,151 +2647,150 @@
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A53" s="6" t="str">
-        <f>+A31</f>
+      <c r="A53" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B53" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C53" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D53" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="E53" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F53" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="G53" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H53" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I53" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="J53" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="K53" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="M53" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="N53" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O53" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A54" s="6" t="str">
+        <f>+A32</f>
         <v>JORDAN RIMMELIN</v>
       </c>
-      <c r="B53" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C53" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="D53" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="E53" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F53" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="G53" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H53" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="I53" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="J53" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K53" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="L53" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M53" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="N53" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O53" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="54" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="20" t="s">
+      <c r="B54" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C54" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D54" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="E54" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F54" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="G54" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H54" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I54" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="J54" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="K54" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="M54" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="N54" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O54" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B54" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C54" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="D54" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="E54" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F54" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="G54" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H54" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="I54" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="J54" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K54" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="L54" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M54" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="N54" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O54" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="55" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A55" s="6" t="s">
+      <c r="B55" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C55" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D55" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="E55" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F55" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="G55" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H55" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I55" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="J55" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="K55" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="M55" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="N55" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O55" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A56" s="6" t="s">
         <v>5</v>
-      </c>
-      <c r="B55" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C55" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="D55" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="E55" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F55" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="G55" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H55" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="I55" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="J55" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K55" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="L55" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M55" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="N55" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O55" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A56" s="6" t="str">
-        <f>+A34</f>
-        <v>MATIAS BERENGUELA</v>
       </c>
       <c r="B56" s="11">
         <v>0.4375</v>
@@ -2835,7 +2838,7 @@
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="str">
         <f>+A35</f>
-        <v>DIEGO MARTINEZ</v>
+        <v>MATIAS BERENGUELA</v>
       </c>
       <c r="B57" s="11">
         <v>0.4375</v>
@@ -2880,440 +2883,441 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A58" s="13" t="s">
+    <row r="58" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A58" s="6" t="str">
+        <f>+A36</f>
+        <v>CAROLINA PEDREROS</v>
+      </c>
+      <c r="B58" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C58" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D58" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="E58" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F58" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="G58" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H58" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I58" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="J58" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="K58" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="M58" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="N58" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O58" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A59" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B58" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C58" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="D58" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="E58" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F58" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="G58" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="H58" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="I58" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="J58" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="K58" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="L58" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="M58" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="N58" s="11" t="s">
-        <v>6</v>
-      </c>
-      <c r="O58" s="11" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="65" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B65" s="14" t="s">
+      <c r="B59" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C59" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="D59" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="E59" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F59" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="G59" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H59" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="I59" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="J59" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="K59" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="M59" s="25" t="s">
+        <v>23</v>
+      </c>
+      <c r="N59" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="O59" s="11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B66" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="C65" s="14"/>
-      <c r="D65" s="14"/>
-      <c r="E65" s="14"/>
-      <c r="F65" s="14"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
-      <c r="I65" s="14"/>
-      <c r="J65" s="14"/>
-      <c r="K65" s="14"/>
-      <c r="L65" s="14"/>
-      <c r="M65" s="14"/>
-      <c r="N65" s="14"/>
-      <c r="O65" s="14"/>
-    </row>
-    <row r="66" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A66" s="1" t="s">
+      <c r="C66" s="14"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
+      <c r="G66" s="14"/>
+      <c r="H66" s="14"/>
+      <c r="I66" s="14"/>
+      <c r="J66" s="14"/>
+      <c r="K66" s="14"/>
+      <c r="L66" s="14"/>
+      <c r="M66" s="14"/>
+      <c r="N66" s="14"/>
+      <c r="O66" s="14"/>
+    </row>
+    <row r="67" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B66" s="15">
+      <c r="B67" s="15">
         <v>46286</v>
       </c>
-      <c r="C66" s="16"/>
-      <c r="D66" s="15">
+      <c r="C67" s="16"/>
+      <c r="D67" s="15">
         <v>46287</v>
       </c>
-      <c r="E66" s="16"/>
-      <c r="F66" s="15">
+      <c r="E67" s="16"/>
+      <c r="F67" s="15">
         <v>46288</v>
       </c>
-      <c r="G66" s="16"/>
-      <c r="H66" s="15">
+      <c r="G67" s="16"/>
+      <c r="H67" s="15">
         <v>46289</v>
       </c>
-      <c r="I66" s="16"/>
-      <c r="J66" s="15">
+      <c r="I67" s="16"/>
+      <c r="J67" s="15">
         <v>46290</v>
       </c>
-      <c r="K66" s="16"/>
-      <c r="L66" s="15">
+      <c r="K67" s="16"/>
+      <c r="L67" s="15">
         <v>46291</v>
       </c>
-      <c r="M66" s="16"/>
-      <c r="N66" s="15">
+      <c r="M67" s="16"/>
+      <c r="N67" s="15">
         <v>46292</v>
       </c>
-      <c r="O66" s="16"/>
-    </row>
-    <row r="67" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="2"/>
-      <c r="B67" s="7" t="s">
+      <c r="O67" s="16"/>
+    </row>
+    <row r="68" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="2"/>
+      <c r="B68" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C67" s="7" t="s">
+      <c r="C68" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D67" s="8" t="s">
+      <c r="D68" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E67" s="8" t="s">
+      <c r="E68" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F67" s="8" t="s">
+      <c r="F68" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="G67" s="8" t="s">
+      <c r="G68" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H67" s="8" t="s">
+      <c r="H68" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="I67" s="8" t="s">
+      <c r="I68" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="J67" s="8" t="s">
+      <c r="J68" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="K67" s="8" t="s">
+      <c r="K68" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="L67" s="8" t="s">
+      <c r="L68" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="M67" s="8" t="s">
+      <c r="M68" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="N67" s="8" t="s">
+      <c r="N68" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="O67" s="8" t="s">
+      <c r="O68" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="68" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A68" s="12" t="str">
-        <f t="shared" ref="A68:A73" si="1">+A45</f>
+    <row r="69" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A69" s="12" t="str">
+        <f t="shared" ref="A69:A74" si="1">+A46</f>
         <v>RAFAEL BUSTOS</v>
       </c>
-      <c r="B68" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C68" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D68" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="E68" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F68" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G68" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H68" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I68" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="J68" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="K68" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L68" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="M68" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N68" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="O68" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-    </row>
-    <row r="69" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="20" t="str">
+      <c r="B69" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C69" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D69" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="E69" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F69" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H69" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I69" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J69" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="K69" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L69" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="M69" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N69" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="O69" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="70" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="20" t="str">
         <f t="shared" si="1"/>
         <v xml:space="preserve">GEISSLEN ERICES </v>
       </c>
-      <c r="B69" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C69" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D69" s="11">
+      <c r="B70" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C70" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D70" s="11">
         <v>0.41666666666666669</v>
       </c>
-      <c r="E69" s="11">
+      <c r="E70" s="11">
         <v>0.83333333333333337</v>
       </c>
-      <c r="F69" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G69" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H69" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I69" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="J69" s="11">
+      <c r="F70" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H70" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I70" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J70" s="11">
         <v>0.41666666666666669</v>
       </c>
-      <c r="K69" s="11">
+      <c r="K70" s="11">
         <v>0.83333333333333337</v>
       </c>
-      <c r="L69" s="11">
+      <c r="L70" s="11">
         <v>0.41666666666666669</v>
       </c>
-      <c r="M69" s="11">
+      <c r="M70" s="11">
         <v>0.83333333333333337</v>
       </c>
-      <c r="N69" s="11">
+      <c r="N70" s="11">
         <v>0.41666666666666669</v>
       </c>
-      <c r="O69" s="11">
+      <c r="O70" s="11">
         <v>0.77083333333333337</v>
       </c>
     </row>
-    <row r="70" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A70" s="6" t="str">
+    <row r="71" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A71" s="6" t="str">
         <f t="shared" si="1"/>
         <v>MAXIMILIANO MEDINA</v>
       </c>
-      <c r="B70" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C70" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D70" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="E70" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F70" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G70" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H70" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I70" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="J70" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="K70" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L70" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="M70" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N70" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="O70" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-    </row>
-    <row r="71" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="20" t="str">
+      <c r="B71" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C71" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D71" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="E71" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F71" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G71" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H71" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I71" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J71" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="K71" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L71" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="M71" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N71" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="O71" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="72" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="20" t="str">
         <f t="shared" si="1"/>
         <v>LISSETTE MORALES</v>
       </c>
-      <c r="B71" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C71" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D71" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="E71" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="F71" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G71" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H71" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I71" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="J71" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="K71" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L71" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="M71" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N71" s="11">
+      <c r="B72" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C72" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D72" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="E72" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="F72" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H72" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I72" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J72" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="K72" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L72" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="M72" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N72" s="11">
         <v>0.41666666666666669</v>
       </c>
-      <c r="O71" s="11">
+      <c r="O72" s="11">
         <v>0.77083333333333337</v>
-      </c>
-    </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A72" s="6" t="str">
-        <f t="shared" si="1"/>
-        <v xml:space="preserve">CRISTIAN MORALES </v>
-      </c>
-      <c r="B72" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C72" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D72" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="E72" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F72" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G72" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H72" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I72" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="J72" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="K72" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L72" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="M72" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N72" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="O72" s="11">
-        <v>0.85416666666666663</v>
       </c>
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="str">
         <f t="shared" si="1"/>
+        <v xml:space="preserve">CRISTIAN MORALES </v>
+      </c>
+      <c r="B73" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C73" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D73" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="E73" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F73" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H73" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I73" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J73" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="K73" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L73" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="M73" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N73" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="O73" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A74" s="6" t="str">
+        <f t="shared" si="1"/>
         <v>DIEGO MARTINEZ</v>
-      </c>
-      <c r="B73" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C73" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D73" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="E73" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F73" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G73" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H73" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I73" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="J73" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="K73" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L73" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="M73" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N73" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="O73" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-    </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A74" s="6" t="s">
-        <v>8</v>
       </c>
       <c r="B74" s="11">
         <v>0.4375</v>
@@ -3360,197 +3364,196 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B75" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C75" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D75" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="E75" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F75" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G75" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H75" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I75" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J75" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="K75" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L75" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="M75" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N75" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="O75" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A76" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B75" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C75" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D75" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="E75" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F75" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G75" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H75" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I75" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="J75" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="K75" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L75" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="M75" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N75" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="O75" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-    </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A76" s="6" t="str">
-        <f>+A53</f>
+      <c r="B76" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C76" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D76" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="E76" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F76" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G76" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I76" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J76" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="K76" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L76" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="M76" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N76" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="O76" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="77" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A77" s="6" t="str">
+        <f>+A54</f>
         <v>JORDAN RIMMELIN</v>
       </c>
-      <c r="B76" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C76" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D76" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="E76" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F76" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G76" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H76" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I76" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="J76" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="K76" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L76" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="M76" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N76" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="O76" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-    </row>
-    <row r="77" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A77" s="20" t="s">
+      <c r="B77" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C77" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D77" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="E77" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F77" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G77" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I77" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J77" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="K77" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L77" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="M77" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N77" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="O77" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B77" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C77" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D77" s="11">
+      <c r="B78" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C78" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D78" s="11">
         <v>0.41666666666666669</v>
       </c>
-      <c r="E77" s="11">
+      <c r="E78" s="11">
         <v>0.83333333333333337</v>
       </c>
-      <c r="F77" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G77" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H77" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I77" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="J77" s="11">
+      <c r="F78" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H78" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I78" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J78" s="11">
         <v>0.41666666666666669</v>
       </c>
-      <c r="K77" s="11">
+      <c r="K78" s="11">
         <v>0.83333333333333337</v>
       </c>
-      <c r="L77" s="11">
+      <c r="L78" s="11">
         <v>0.41666666666666669</v>
       </c>
-      <c r="M77" s="11">
+      <c r="M78" s="11">
         <v>0.83333333333333337</v>
       </c>
-      <c r="N77" s="11">
+      <c r="N78" s="11">
         <v>0.45833333333333331</v>
       </c>
-      <c r="O77" s="11">
+      <c r="O78" s="11">
         <v>0.8125</v>
       </c>
     </row>
-    <row r="78" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A78" s="6" t="s">
+    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A79" s="6" t="s">
         <v>5</v>
-      </c>
-      <c r="B78" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C78" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D78" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="E78" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F78" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G78" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H78" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I78" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="J78" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="K78" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L78" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="M78" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N78" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="O78" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-    </row>
-    <row r="79" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A79" s="6" t="str">
-        <f>+A56</f>
-        <v>MATIAS BERENGUELA</v>
       </c>
       <c r="B79" s="11">
         <v>0.4375</v>
@@ -3598,7 +3601,7 @@
     <row r="80" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="str">
         <f>+A57</f>
-        <v>DIEGO MARTINEZ</v>
+        <v>MATIAS BERENGUELA</v>
       </c>
       <c r="B80" s="11">
         <v>0.4375</v>
@@ -3643,440 +3646,441 @@
         <v>0.85416666666666663</v>
       </c>
     </row>
-    <row r="81" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="13" t="s">
+    <row r="81" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A81" s="6" t="str">
+        <f>+A58</f>
+        <v>CAROLINA PEDREROS</v>
+      </c>
+      <c r="B81" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C81" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D81" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="E81" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F81" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H81" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I81" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J81" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="K81" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L81" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="M81" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N81" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="O81" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="82" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A82" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B81" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C81" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D81" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="E81" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F81" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G81" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H81" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="I81" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="J81" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="K81" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L81" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="M81" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N81" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="O81" s="11">
-        <v>0.85416666666666663</v>
-      </c>
-    </row>
-    <row r="87" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B87" s="14" t="s">
+      <c r="B82" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C82" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D82" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="E82" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="F82" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="I82" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="J82" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="K82" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L82" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="M82" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N82" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="O82" s="11">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="88" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B88" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="C87" s="14"/>
-      <c r="D87" s="14"/>
-      <c r="E87" s="14"/>
-      <c r="F87" s="14"/>
-      <c r="G87" s="14"/>
-      <c r="H87" s="14"/>
-      <c r="I87" s="14"/>
-      <c r="J87" s="14"/>
-      <c r="K87" s="14"/>
-      <c r="L87" s="14"/>
-      <c r="M87" s="14"/>
-      <c r="N87" s="14"/>
-      <c r="O87" s="14"/>
-    </row>
-    <row r="88" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="1" t="s">
+      <c r="C88" s="14"/>
+      <c r="D88" s="14"/>
+      <c r="E88" s="14"/>
+      <c r="F88" s="14"/>
+      <c r="G88" s="14"/>
+      <c r="H88" s="14"/>
+      <c r="I88" s="14"/>
+      <c r="J88" s="14"/>
+      <c r="K88" s="14"/>
+      <c r="L88" s="14"/>
+      <c r="M88" s="14"/>
+      <c r="N88" s="14"/>
+      <c r="O88" s="14"/>
+    </row>
+    <row r="89" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A89" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B88" s="15">
+      <c r="B89" s="15">
         <v>46293</v>
       </c>
-      <c r="C88" s="16"/>
-      <c r="D88" s="15">
+      <c r="C89" s="16"/>
+      <c r="D89" s="15">
         <v>46294</v>
       </c>
-      <c r="E88" s="16"/>
-      <c r="F88" s="15">
+      <c r="E89" s="16"/>
+      <c r="F89" s="15">
         <v>46295</v>
       </c>
-      <c r="G88" s="16"/>
-      <c r="H88" s="15">
+      <c r="G89" s="16"/>
+      <c r="H89" s="15">
         <v>46296</v>
       </c>
-      <c r="I88" s="16"/>
-      <c r="J88" s="15">
+      <c r="I89" s="16"/>
+      <c r="J89" s="15">
         <v>46297</v>
       </c>
-      <c r="K88" s="16"/>
-      <c r="L88" s="15">
+      <c r="K89" s="16"/>
+      <c r="L89" s="15">
         <v>46298</v>
       </c>
-      <c r="M88" s="16"/>
-      <c r="N88" s="15">
+      <c r="M89" s="16"/>
+      <c r="N89" s="15">
         <v>46299</v>
       </c>
-      <c r="O88" s="16"/>
-    </row>
-    <row r="89" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A89" s="2"/>
-      <c r="B89" s="7" t="s">
+      <c r="O89" s="16"/>
+    </row>
+    <row r="90" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A90" s="2"/>
+      <c r="B90" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="C89" s="7" t="s">
+      <c r="C90" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="D89" s="8" t="s">
+      <c r="D90" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="E89" s="8" t="s">
+      <c r="E90" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="F89" s="8" t="s">
+      <c r="F90" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="G89" s="8" t="s">
+      <c r="G90" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="H89" s="8" t="s">
+      <c r="H90" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="I89" s="8" t="s">
+      <c r="I90" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="J89" s="8" t="s">
+      <c r="J90" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="K89" s="8" t="s">
+      <c r="K90" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="L89" s="8" t="s">
+      <c r="L90" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="M89" s="8" t="s">
+      <c r="M90" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="N89" s="8" t="s">
+      <c r="N90" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="O89" s="8" t="s">
+      <c r="O90" s="8" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A90" s="12" t="str">
-        <f t="shared" ref="A90:A95" si="2">+A68</f>
+    <row r="91" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A91" s="12" t="str">
+        <f t="shared" ref="A91:A96" si="2">+A69</f>
         <v>RAFAEL BUSTOS</v>
       </c>
-      <c r="B90" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C90" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D90" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E90" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F90" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G90" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H90" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="I90" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="J90" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="K90" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L90" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="M90" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N90" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="O90" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-    </row>
-    <row r="91" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="20" t="str">
+      <c r="B91" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C91" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D91" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E91" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F91" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H91" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="I91" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="J91" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="K91" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L91" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="M91" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N91" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="O91" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="92" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="20" t="str">
         <f t="shared" si="2"/>
         <v xml:space="preserve">GEISSLEN ERICES </v>
       </c>
-      <c r="B91" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C91" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D91" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E91" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F91" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G91" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H91" s="21">
+      <c r="B92" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C92" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D92" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E92" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F92" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G92" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H92" s="21">
         <v>0.41666666666666669</v>
       </c>
-      <c r="I91" s="21">
+      <c r="I92" s="21">
         <v>0.83333333333333337</v>
       </c>
-      <c r="J91" s="21">
+      <c r="J92" s="21">
         <v>0.41666666666666669</v>
       </c>
-      <c r="K91" s="21">
+      <c r="K92" s="21">
         <v>0.83333333333333337</v>
       </c>
-      <c r="L91" s="21">
+      <c r="L92" s="21">
         <v>0.41666666666666669</v>
       </c>
-      <c r="M91" s="21">
+      <c r="M92" s="21">
         <v>0.83333333333333337</v>
       </c>
-      <c r="N91" s="21">
+      <c r="N92" s="21">
         <v>0.41666666666666669</v>
       </c>
-      <c r="O91" s="21">
+      <c r="O92" s="21">
         <v>0.77083333333333337</v>
       </c>
     </row>
-    <row r="92" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A92" s="6" t="str">
+    <row r="93" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A93" s="6" t="str">
         <f t="shared" si="2"/>
         <v>MAXIMILIANO MEDINA</v>
       </c>
-      <c r="B92" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C92" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D92" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E92" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F92" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G92" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H92" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="I92" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="J92" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="K92" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L92" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="M92" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N92" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="O92" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-    </row>
-    <row r="93" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="20" t="str">
+      <c r="B93" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C93" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D93" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E93" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F93" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G93" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H93" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="I93" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="J93" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="K93" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L93" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="M93" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N93" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="O93" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="94" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="20" t="str">
         <f t="shared" si="2"/>
         <v>LISSETTE MORALES</v>
       </c>
-      <c r="B93" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C93" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D93" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E93" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F93" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G93" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H93" s="21">
+      <c r="B94" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C94" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D94" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E94" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F94" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G94" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H94" s="21">
         <v>0.41666666666666669</v>
       </c>
-      <c r="I93" s="21">
+      <c r="I94" s="21">
         <v>0.83333333333333337</v>
       </c>
-      <c r="J93" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="K93" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L93" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="M93" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N93" s="21">
+      <c r="J94" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="K94" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L94" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="M94" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N94" s="21">
         <v>0.45833333333333331</v>
       </c>
-      <c r="O93" s="21">
+      <c r="O94" s="21">
         <v>0.8125</v>
-      </c>
-    </row>
-    <row r="94" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A94" s="6" t="str">
-        <f t="shared" si="2"/>
-        <v xml:space="preserve">CRISTIAN MORALES </v>
-      </c>
-      <c r="B94" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C94" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D94" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E94" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F94" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G94" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H94" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="I94" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="J94" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="K94" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L94" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="M94" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N94" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="O94" s="21">
-        <v>0.85416666666666663</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="str">
         <f t="shared" si="2"/>
+        <v xml:space="preserve">CRISTIAN MORALES </v>
+      </c>
+      <c r="B95" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C95" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D95" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E95" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F95" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G95" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H95" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="I95" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="J95" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="K95" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L95" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="M95" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N95" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="O95" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A96" s="6" t="str">
+        <f t="shared" si="2"/>
         <v>DIEGO MARTINEZ</v>
-      </c>
-      <c r="B95" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C95" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D95" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E95" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F95" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G95" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H95" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="I95" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="J95" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="K95" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L95" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="M95" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N95" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="O95" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-    </row>
-    <row r="96" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A96" s="6" t="s">
-        <v>8</v>
       </c>
       <c r="B96" s="11">
         <v>0.4375</v>
@@ -4123,197 +4127,196 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B97" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C97" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D97" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E97" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F97" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G97" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H97" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="I97" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="J97" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="K97" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L97" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="M97" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N97" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="O97" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A98" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B97" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C97" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D97" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E97" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F97" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G97" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H97" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="I97" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="J97" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="K97" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L97" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="M97" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N97" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="O97" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-    </row>
-    <row r="98" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A98" s="6" t="str">
-        <f>+A76</f>
+      <c r="B98" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C98" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D98" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E98" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F98" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G98" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H98" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="I98" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="J98" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="K98" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L98" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="M98" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N98" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="O98" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="99" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A99" s="6" t="str">
+        <f>+A77</f>
         <v>JORDAN RIMMELIN</v>
       </c>
-      <c r="B98" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C98" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D98" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E98" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F98" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G98" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H98" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="I98" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="J98" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="K98" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L98" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="M98" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N98" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="O98" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-    </row>
-    <row r="99" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="20" t="s">
+      <c r="B99" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C99" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D99" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E99" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F99" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G99" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H99" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="I99" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="J99" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="K99" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L99" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="M99" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N99" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="O99" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="100" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="B99" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C99" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D99" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E99" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F99" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G99" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H99" s="21">
+      <c r="B100" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C100" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D100" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E100" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F100" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G100" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H100" s="21">
         <v>0.41666666666666669</v>
       </c>
-      <c r="I99" s="21">
+      <c r="I100" s="21">
         <v>0.83333333333333337</v>
       </c>
-      <c r="J99" s="21">
+      <c r="J100" s="21">
         <v>0.41666666666666669</v>
       </c>
-      <c r="K99" s="21">
+      <c r="K100" s="21">
         <v>0.83333333333333337</v>
       </c>
-      <c r="L99" s="21">
+      <c r="L100" s="21">
         <v>0.41666666666666669</v>
       </c>
-      <c r="M99" s="21">
+      <c r="M100" s="21">
         <v>0.83333333333333337</v>
       </c>
-      <c r="N99" s="21">
+      <c r="N100" s="21">
         <v>0.41666666666666669</v>
       </c>
-      <c r="O99" s="21">
+      <c r="O100" s="21">
         <v>0.77083333333333337</v>
       </c>
     </row>
-    <row r="100" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A100" s="6" t="s">
+    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A101" s="6" t="s">
         <v>5</v>
-      </c>
-      <c r="B100" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C100" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D100" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E100" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F100" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G100" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H100" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="I100" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="J100" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="K100" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L100" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="M100" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N100" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="O100" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-    </row>
-    <row r="101" spans="1:15" x14ac:dyDescent="0.3">
-      <c r="A101" s="6" t="str">
-        <f>+A79</f>
-        <v>MATIAS BERENGUELA</v>
       </c>
       <c r="B101" s="11">
         <v>0.4375</v>
@@ -4361,7 +4364,7 @@
     <row r="102" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="str">
         <f>+A80</f>
-        <v>DIEGO MARTINEZ</v>
+        <v>MATIAS BERENGUELA</v>
       </c>
       <c r="B102" s="11">
         <v>0.4375</v>
@@ -4406,87 +4409,135 @@
         <v>0.85416666666666663</v>
       </c>
     </row>
-    <row r="103" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="13" t="s">
+    <row r="103" spans="1:15" x14ac:dyDescent="0.3">
+      <c r="A103" s="6" t="str">
+        <f>+A81</f>
+        <v>CAROLINA PEDREROS</v>
+      </c>
+      <c r="B103" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C103" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D103" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E103" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F103" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G103" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H103" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="I103" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="J103" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="K103" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L103" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="M103" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N103" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="O103" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+    </row>
+    <row r="104" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B103" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="C103" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="D103" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="E103" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F103" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="G103" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="H103" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="I103" s="11">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="J103" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="K103" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="L103" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="M103" s="21">
-        <v>0.85416666666666663</v>
-      </c>
-      <c r="N103" s="21">
-        <v>0.4375</v>
-      </c>
-      <c r="O103" s="21">
+      <c r="B104" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="C104" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="D104" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="E104" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="F104" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="G104" s="10" t="s">
+        <v>6</v>
+      </c>
+      <c r="H104" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="I104" s="11">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="J104" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="K104" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="L104" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="M104" s="21">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="N104" s="21">
+        <v>0.4375</v>
+      </c>
+      <c r="O104" s="21">
         <v>0.85416666666666663</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="B87:O87"/>
-    <mergeCell ref="B88:C88"/>
-    <mergeCell ref="D88:E88"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="H88:I88"/>
-    <mergeCell ref="J88:K88"/>
-    <mergeCell ref="L88:M88"/>
-    <mergeCell ref="N88:O88"/>
-    <mergeCell ref="B65:O65"/>
-    <mergeCell ref="B66:C66"/>
-    <mergeCell ref="D66:E66"/>
-    <mergeCell ref="F66:G66"/>
-    <mergeCell ref="H66:I66"/>
-    <mergeCell ref="J66:K66"/>
-    <mergeCell ref="L66:M66"/>
-    <mergeCell ref="N66:O66"/>
-    <mergeCell ref="B42:O42"/>
-    <mergeCell ref="B43:C43"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="J43:K43"/>
-    <mergeCell ref="L43:M43"/>
-    <mergeCell ref="N43:O43"/>
-    <mergeCell ref="B20:O20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="H21:I21"/>
-    <mergeCell ref="J21:K21"/>
-    <mergeCell ref="L21:M21"/>
-    <mergeCell ref="N21:O21"/>
+    <mergeCell ref="B88:O88"/>
+    <mergeCell ref="B89:C89"/>
+    <mergeCell ref="D89:E89"/>
+    <mergeCell ref="F89:G89"/>
+    <mergeCell ref="H89:I89"/>
+    <mergeCell ref="J89:K89"/>
+    <mergeCell ref="L89:M89"/>
+    <mergeCell ref="N89:O89"/>
+    <mergeCell ref="B66:O66"/>
+    <mergeCell ref="B67:C67"/>
+    <mergeCell ref="D67:E67"/>
+    <mergeCell ref="F67:G67"/>
+    <mergeCell ref="H67:I67"/>
+    <mergeCell ref="J67:K67"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="N67:O67"/>
+    <mergeCell ref="B43:O43"/>
+    <mergeCell ref="B44:C44"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="F44:G44"/>
+    <mergeCell ref="H44:I44"/>
+    <mergeCell ref="J44:K44"/>
+    <mergeCell ref="L44:M44"/>
+    <mergeCell ref="N44:O44"/>
+    <mergeCell ref="B21:O21"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="J22:K22"/>
+    <mergeCell ref="L22:M22"/>
+    <mergeCell ref="N22:O22"/>
     <mergeCell ref="B1:O1"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>

--- a/horarios.xlsx
+++ b/horarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dreame\Desktop\Claude\Dreame\Turnos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3F748EE-CEBD-4246-A31F-C935336E39EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA19CC1-238A-498C-A400-CD52914FBF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="452" uniqueCount="24">
   <si>
     <t>Promotor</t>
   </si>
@@ -45,9 +45,6 @@
   </si>
   <si>
     <t>Salida</t>
-  </si>
-  <si>
-    <t>ROMINA MANSILLA</t>
   </si>
   <si>
     <t>CESAR CASTILLO</t>
@@ -686,7 +683,7 @@
   <sheetData>
     <row r="1" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B1" s="14" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C1" s="14"/>
       <c r="D1" s="14"/>
@@ -782,7 +779,7 @@
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A4" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B4" s="9">
         <v>0.4375</v>
@@ -797,16 +794,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H4" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I4" s="9" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J4" s="9">
         <v>0.4375</v>
@@ -831,7 +828,7 @@
     </row>
     <row r="5" spans="1:18" s="22" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A5" s="20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B5" s="21">
         <v>0.4375</v>
@@ -846,16 +843,16 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="F5" s="21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G5" s="21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H5" s="21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I5" s="21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J5" s="21">
         <v>0.41666666666666669</v>
@@ -880,7 +877,7 @@
     </row>
     <row r="6" spans="1:18" s="22" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A6" s="20" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B6" s="21">
         <v>0.4375</v>
@@ -895,16 +892,16 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6" s="24" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H6" s="21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I6" s="21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J6" s="21">
         <v>0.41666666666666669</v>
@@ -929,7 +926,7 @@
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" s="11">
         <v>0.4375</v>
@@ -944,16 +941,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I7" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J7" s="11">
         <v>0.4375</v>
@@ -978,7 +975,7 @@
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" s="11">
         <v>0.4375</v>
@@ -993,16 +990,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H8" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I8" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J8" s="11">
         <v>0.4375</v>
@@ -1027,7 +1024,7 @@
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B9" s="11">
         <v>0.4375</v>
@@ -1042,16 +1039,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H9" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I9" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J9" s="11">
         <v>0.4375</v>
@@ -1076,7 +1073,7 @@
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B10" s="11">
         <v>0.4375</v>
@@ -1091,16 +1088,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H10" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I10" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J10" s="11">
         <v>0.4375</v>
@@ -1125,7 +1122,7 @@
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B11" s="11">
         <v>0.4375</v>
@@ -1140,16 +1137,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H11" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I11" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J11" s="11">
         <v>0.4375</v>
@@ -1174,7 +1171,7 @@
     </row>
     <row r="12" spans="1:18" s="22" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A12" s="20" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B12" s="21">
         <v>0.4375</v>
@@ -1189,16 +1186,16 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G12" s="21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H12" s="21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I12" s="21" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J12" s="21">
         <v>0.41666666666666669</v>
@@ -1221,7 +1218,7 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B13" s="11">
         <v>0.4375</v>
@@ -1236,16 +1233,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F13" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I13" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J13" s="11">
         <v>0.4375</v>
@@ -1268,7 +1265,7 @@
     </row>
     <row r="14" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A14" s="13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B14" s="11">
         <v>0.4375</v>
@@ -1283,16 +1280,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F14" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I14" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J14" s="11">
         <v>0.4375</v>
@@ -1315,7 +1312,7 @@
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A15" s="17" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" s="11">
         <v>0.4375</v>
@@ -1330,16 +1327,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I15" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J15" s="11">
         <v>0.4375</v>
@@ -1362,7 +1359,7 @@
     </row>
     <row r="16" spans="1:18" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A16" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B16" s="19">
         <v>0.4375</v>
@@ -1377,16 +1374,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F16" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I16" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J16" s="11">
         <v>0.4375</v>
@@ -1409,7 +1406,7 @@
     </row>
     <row r="17" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A17" s="18" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B17" s="19">
         <v>0.4375</v>
@@ -1424,16 +1421,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F17" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G17" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H17" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I17" s="19" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J17" s="11">
         <v>0.4375</v>
@@ -1456,7 +1453,7 @@
     </row>
     <row r="21" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B21" s="14" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
@@ -1562,10 +1559,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D24" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F24" s="21">
         <v>0.4375</v>
@@ -1592,10 +1589,10 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="N24" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O24" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
@@ -1610,10 +1607,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D25" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F25" s="21">
         <v>0.4375</v>
@@ -1640,15 +1637,15 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N25" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O25" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B26" s="21">
         <v>0.4375</v>
@@ -1657,10 +1654,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D26" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F26" s="21">
         <v>0.4375</v>
@@ -1687,10 +1684,10 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="N26" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O26" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="27" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
@@ -1705,10 +1702,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D27" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F27" s="21">
         <v>0.4375</v>
@@ -1735,10 +1732,10 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N27" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O27" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.3">
@@ -1753,10 +1750,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D28" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F28" s="21">
         <v>0.4375</v>
@@ -1783,10 +1780,10 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="N28" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O28" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.3">
@@ -1801,10 +1798,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F29" s="21">
         <v>0.4375</v>
@@ -1831,15 +1828,15 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="N29" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O29" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B30" s="21">
         <v>0.4375</v>
@@ -1848,10 +1845,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D30" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F30" s="21">
         <v>0.4375</v>
@@ -1878,15 +1875,15 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="N30" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O30" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B31" s="21">
         <v>0.4375</v>
@@ -1895,10 +1892,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F31" s="21">
         <v>0.4375</v>
@@ -1925,10 +1922,10 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="N31" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O31" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.3">
@@ -1943,10 +1940,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F32" s="21">
         <v>0.4375</v>
@@ -1973,15 +1970,15 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="N32" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O32" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A33" s="20" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B33" s="21">
         <v>0.4375</v>
@@ -1990,10 +1987,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F33" s="21">
         <v>0.4375</v>
@@ -2020,15 +2017,15 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="N33" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O33" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B34" s="21">
         <v>0.4375</v>
@@ -2037,10 +2034,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D34" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F34" s="21">
         <v>0.4375</v>
@@ -2067,15 +2064,15 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="N34" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O34" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B35" s="21">
         <v>0.4375</v>
@@ -2084,10 +2081,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D35" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F35" s="21">
         <v>0.4375</v>
@@ -2114,10 +2111,10 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="N35" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O35" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.3">
@@ -2132,10 +2129,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F36" s="21">
         <v>0.4375</v>
@@ -2162,15 +2159,15 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="N36" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O36" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="37" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A37" s="13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B37" s="21">
         <v>0.4375</v>
@@ -2179,10 +2176,10 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F37" s="21">
         <v>0.4375</v>
@@ -2209,15 +2206,15 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="N37" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O37" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="43" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B43" s="14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C43" s="14"/>
       <c r="D43" s="14"/>
@@ -2335,28 +2332,28 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I46" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J46" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K46" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L46" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M46" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N46" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O46" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
@@ -2383,28 +2380,28 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I47" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J47" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K47" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L47" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M47" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N47" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O47" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.3">
@@ -2431,28 +2428,28 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I48" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J48" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K48" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L48" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M48" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N48" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O48" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="49" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
@@ -2479,28 +2476,28 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I49" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J49" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K49" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L49" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M49" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N49" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O49" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.3">
@@ -2527,28 +2524,28 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I50" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J50" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K50" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L50" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M50" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N50" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O50" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.3">
@@ -2575,33 +2572,33 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="H51" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I51" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J51" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K51" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L51" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M51" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N51" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O51" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B52" s="11">
         <v>0.4375</v>
@@ -2622,33 +2619,33 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I52" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J52" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K52" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L52" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M52" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N52" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O52" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B53" s="11">
         <v>0.4375</v>
@@ -2669,28 +2666,28 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="H53" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I53" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J53" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K53" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L53" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M53" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N53" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O53" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.3">
@@ -2717,33 +2714,33 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="H54" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I54" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J54" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K54" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L54" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M54" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N54" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O54" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="55" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A55" s="20" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B55" s="11">
         <v>0.4375</v>
@@ -2764,33 +2761,33 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="H55" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I55" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J55" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K55" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L55" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M55" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N55" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O55" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B56" s="11">
         <v>0.4375</v>
@@ -2811,28 +2808,28 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="H56" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I56" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J56" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K56" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L56" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M56" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N56" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O56" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.3">
@@ -2859,28 +2856,28 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="H57" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I57" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J57" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K57" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L57" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M57" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N57" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O57" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.3">
@@ -2907,33 +2904,33 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="H58" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I58" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J58" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K58" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L58" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M58" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N58" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O58" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A59" s="13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B59" s="11">
         <v>0.4375</v>
@@ -2954,33 +2951,33 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="H59" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I59" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J59" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K59" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L59" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M59" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N59" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="O59" s="11" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B66" s="14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C66" s="14"/>
       <c r="D66" s="14"/>
@@ -3092,16 +3089,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F69" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G69" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H69" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I69" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J69" s="11">
         <v>0.4375</v>
@@ -3140,16 +3137,16 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="F70" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G70" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H70" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I70" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J70" s="11">
         <v>0.41666666666666669</v>
@@ -3188,16 +3185,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F71" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G71" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H71" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I71" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J71" s="11">
         <v>0.4375</v>
@@ -3236,16 +3233,16 @@
         <v>0.85416666666666663</v>
       </c>
       <c r="F72" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G72" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H72" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I72" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J72" s="11">
         <v>0.4375</v>
@@ -3284,16 +3281,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F73" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G73" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H73" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I73" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J73" s="11">
         <v>0.4375</v>
@@ -3332,16 +3329,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F74" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G74" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H74" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I74" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J74" s="11">
         <v>0.4375</v>
@@ -3364,7 +3361,7 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B75" s="11">
         <v>0.4375</v>
@@ -3379,16 +3376,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F75" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G75" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H75" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I75" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J75" s="11">
         <v>0.4375</v>
@@ -3411,7 +3408,7 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B76" s="11">
         <v>0.4375</v>
@@ -3426,16 +3423,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F76" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G76" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H76" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I76" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J76" s="11">
         <v>0.4375</v>
@@ -3474,16 +3471,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F77" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G77" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H77" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I77" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J77" s="11">
         <v>0.4375</v>
@@ -3506,7 +3503,7 @@
     </row>
     <row r="78" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A78" s="20" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B78" s="11">
         <v>0.4375</v>
@@ -3521,16 +3518,16 @@
         <v>0.83333333333333337</v>
       </c>
       <c r="F78" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G78" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H78" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I78" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J78" s="11">
         <v>0.41666666666666669</v>
@@ -3553,7 +3550,7 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B79" s="11">
         <v>0.4375</v>
@@ -3568,16 +3565,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F79" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G79" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H79" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I79" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J79" s="11">
         <v>0.4375</v>
@@ -3616,16 +3613,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F80" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G80" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H80" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I80" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J80" s="11">
         <v>0.4375</v>
@@ -3664,16 +3661,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F81" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G81" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H81" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I81" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J81" s="11">
         <v>0.4375</v>
@@ -3696,7 +3693,7 @@
     </row>
     <row r="82" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A82" s="13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B82" s="11">
         <v>0.4375</v>
@@ -3711,16 +3708,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="F82" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G82" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H82" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="I82" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J82" s="11">
         <v>0.4375</v>
@@ -3743,7 +3740,7 @@
     </row>
     <row r="88" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B88" s="14" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C88" s="14"/>
       <c r="D88" s="14"/>
@@ -3849,16 +3846,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E91" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F91" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G91" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H91" s="11">
         <v>0.4375</v>
@@ -3897,16 +3894,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E92" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F92" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G92" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H92" s="21">
         <v>0.41666666666666669</v>
@@ -3945,16 +3942,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E93" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F93" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G93" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H93" s="11">
         <v>0.4375</v>
@@ -3993,16 +3990,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E94" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F94" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G94" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H94" s="21">
         <v>0.41666666666666669</v>
@@ -4041,16 +4038,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E95" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F95" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G95" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H95" s="11">
         <v>0.4375</v>
@@ -4089,16 +4086,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E96" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F96" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G96" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H96" s="11">
         <v>0.4375</v>
@@ -4127,7 +4124,7 @@
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B97" s="11">
         <v>0.4375</v>
@@ -4136,16 +4133,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E97" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F97" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G97" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H97" s="11">
         <v>0.4375</v>
@@ -4174,7 +4171,7 @@
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
-        <v>3</v>
+        <v>21</v>
       </c>
       <c r="B98" s="11">
         <v>0.4375</v>
@@ -4183,16 +4180,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E98" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F98" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G98" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H98" s="11">
         <v>0.4375</v>
@@ -4231,16 +4228,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E99" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F99" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G99" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H99" s="11">
         <v>0.4375</v>
@@ -4269,7 +4266,7 @@
     </row>
     <row r="100" spans="1:15" s="22" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A100" s="20" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B100" s="11">
         <v>0.4375</v>
@@ -4278,16 +4275,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E100" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F100" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G100" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H100" s="21">
         <v>0.41666666666666669</v>
@@ -4316,7 +4313,7 @@
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B101" s="11">
         <v>0.4375</v>
@@ -4325,16 +4322,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E101" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F101" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G101" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H101" s="11">
         <v>0.4375</v>
@@ -4373,16 +4370,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E102" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F102" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G102" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H102" s="11">
         <v>0.4375</v>
@@ -4421,16 +4418,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E103" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F103" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G103" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H103" s="11">
         <v>0.4375</v>
@@ -4459,7 +4456,7 @@
     </row>
     <row r="104" spans="1:15" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A104" s="13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B104" s="11">
         <v>0.4375</v>
@@ -4468,16 +4465,16 @@
         <v>0.79166666666666663</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E104" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F104" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G104" s="10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H104" s="11">
         <v>0.4375</v>

--- a/horarios.xlsx
+++ b/horarios.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dreame\Desktop\Claude\Dreame\Turnos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBA19CC1-238A-498C-A400-CD52914FBF27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F75135AA-4D0F-488E-AD0E-680754A32F21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -651,28 +651,6 @@
 </a:theme>
 </file>
 
-<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
-<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="438" row="0">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </wetp:taskpane>
-</wetp:taskpanes>
-</file>
-
-<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{480BFDE9-F627-45B4-9498-9B8FAA65FAC7}">
-  <we:reference id="wa200009404" version="1.0.0.8" store="es-MX" storeType="OMEX"/>
-  <we:alternateReferences>
-    <we:reference id="wa200009404" version="1.0.0.8" store="wa200009404" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties>
-    <we:property name="claude.fileId" value="&quot;57165eac-a553-47d9-a6a5-046e4f2f8b35&quot;"/>
-  </we:properties>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3DB7FB46-34C8-4ECD-A089-0D01F6EF7C8B}">
   <dimension ref="A1:R104"/>
@@ -787,29 +765,29 @@
       <c r="C4" s="9">
         <v>0.79166666666666663</v>
       </c>
-      <c r="D4" s="9">
-        <v>0.4375</v>
-      </c>
-      <c r="E4" s="9">
-        <v>0.79166666666666663</v>
-      </c>
-      <c r="F4" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="I4" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="J4" s="9">
-        <v>0.4375</v>
-      </c>
-      <c r="K4" s="9">
-        <v>0.85416666666666663</v>
+      <c r="D4" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="F4" s="9">
+        <v>0.4375</v>
+      </c>
+      <c r="G4" s="9">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="H4" s="9">
+        <v>0.4375</v>
+      </c>
+      <c r="I4" s="9">
+        <v>0.85416666666666663</v>
+      </c>
+      <c r="J4" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="K4" s="9" t="s">
+        <v>5</v>
       </c>
       <c r="L4" s="11">
         <v>0.4375</v>
@@ -3280,11 +3258,11 @@
       <c r="E73" s="11">
         <v>0.79166666666666663</v>
       </c>
-      <c r="F73" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="G73" s="10" t="s">
-        <v>5</v>
+      <c r="F73" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="G73" s="11">
+        <v>0.85416666666666663</v>
       </c>
       <c r="H73" s="10" t="s">
         <v>5</v>
@@ -3292,11 +3270,11 @@
       <c r="I73" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="J73" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="K73" s="11">
-        <v>0.85416666666666663</v>
+      <c r="J73" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="K73" s="10" t="s">
+        <v>5</v>
       </c>
       <c r="L73" s="11">
         <v>0.4375</v>
@@ -3416,11 +3394,11 @@
       <c r="C76" s="11">
         <v>0.79166666666666663</v>
       </c>
-      <c r="D76" s="11">
-        <v>0.4375</v>
-      </c>
-      <c r="E76" s="11">
-        <v>0.79166666666666663</v>
+      <c r="D76" s="10" t="s">
+        <v>5</v>
+      </c>
+      <c r="E76" s="10" t="s">
+        <v>5</v>
       </c>
       <c r="F76" s="10" t="s">
         <v>5</v>
@@ -3428,11 +3406,11 @@
       <c r="G76" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="H76" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="I76" s="10" t="s">
-        <v>5</v>
+      <c r="H76" s="11">
+        <v>0.4375</v>
+      </c>
+      <c r="I76" s="11">
+        <v>0.79166666666666663</v>
       </c>
       <c r="J76" s="11">
         <v>0.4375</v>
